--- a/Financial Analysis/BAND.xlsx
+++ b/Financial Analysis/BAND.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3690A7-1EA1-4209-B237-0D7C1F36B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C09C42B-AD6C-4C30-99FD-264EA6EDCB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{051CBDE9-D4CF-414F-808E-F0CC5F126926}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{051CBDE9-D4CF-414F-808E-F0CC5F126926}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +257,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -296,6 +305,8 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -367,13 +378,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -391,8 +402,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5440680" y="7620"/>
-          <a:ext cx="0" cy="9060180"/>
+          <a:off x="6050280" y="7620"/>
+          <a:ext cx="0" cy="9425940"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -741,17 +752,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>17.52</v>
+        <v>16.11</v>
       </c>
       <c r="E3" s="3">
-        <v>45927</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45928</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="3">
-        <v>45960</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -759,11 +770,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>28.1</f>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -772,7 +783,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>492.31200000000001</v>
+        <v>492.96600000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -780,11 +791,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>60.1+8</f>
-        <v>68.099999999999994</v>
+        <f>73.4+7</f>
+        <v>80.400000000000006</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -792,11 +803,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>7.6+247</f>
-        <v>254.6</v>
+        <f>7.6+247.3</f>
+        <v>254.9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -805,7 +816,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-186.5</v>
+        <v>-174.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -814,7 +825,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>678.81200000000001</v>
+        <v>667.46600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -934,11 +945,11 @@
         <v>180</v>
       </c>
       <c r="I3" s="8">
-        <v>190</v>
+        <v>191.9</v>
       </c>
       <c r="J3" s="8">
-        <f>F3*1.01</f>
-        <v>212.1</v>
+        <f>F3*0.99</f>
+        <v>207.9</v>
       </c>
       <c r="L3" s="8">
         <v>232.6</v>
@@ -960,47 +971,47 @@
       </c>
       <c r="R3" s="8">
         <f>SUM(G3:J3)</f>
-        <v>756.4</v>
+        <v>754.1</v>
       </c>
       <c r="S3" s="8">
-        <f>R3*1.03</f>
-        <v>779.09199999999998</v>
+        <f>R3*1.02</f>
+        <v>769.18200000000002</v>
       </c>
       <c r="T3" s="8">
         <f t="shared" ref="T3:AB3" si="0">S3*1.02</f>
-        <v>794.67384000000004</v>
+        <v>784.56564000000003</v>
       </c>
       <c r="U3" s="8">
         <f t="shared" si="0"/>
-        <v>810.56731680000007</v>
+        <v>800.25695280000002</v>
       </c>
       <c r="V3" s="8">
         <f t="shared" si="0"/>
-        <v>826.77866313600009</v>
+        <v>816.26209185599998</v>
       </c>
       <c r="W3" s="8">
         <f t="shared" si="0"/>
-        <v>843.31423639872014</v>
+        <v>832.58733369311994</v>
       </c>
       <c r="X3" s="8">
         <f t="shared" si="0"/>
-        <v>860.18052112669454</v>
+        <v>849.23908036698231</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" si="0"/>
-        <v>877.38413154922841</v>
+        <v>866.22386197432195</v>
       </c>
       <c r="Z3" s="8">
         <f t="shared" si="0"/>
-        <v>894.931814180213</v>
+        <v>883.54833921380839</v>
       </c>
       <c r="AA3" s="8">
         <f t="shared" si="0"/>
-        <v>912.83045046381721</v>
+        <v>901.21930599808456</v>
       </c>
       <c r="AB3" s="8">
         <f t="shared" si="0"/>
-        <v>931.08705947309363</v>
+        <v>919.24369211804628</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.3">
@@ -1027,12 +1038,11 @@
         <v>108.3</v>
       </c>
       <c r="I4" s="5">
-        <f>I3-I5</f>
-        <v>112.10000000000001</v>
+        <v>118.1</v>
       </c>
       <c r="J4" s="5">
         <f>J3-J5</f>
-        <v>129.381</v>
+        <v>126.819</v>
       </c>
       <c r="L4" s="5">
         <v>125</v>
@@ -1054,47 +1064,47 @@
       </c>
       <c r="R4" s="5">
         <f>SUM(G4:J4)</f>
-        <v>452.48099999999999</v>
+        <v>455.91900000000004</v>
       </c>
       <c r="S4" s="5">
         <f>S3-S5</f>
-        <v>451.87335999999999</v>
+        <v>446.12556000000001</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:AB4" si="1">T3-T5</f>
-        <v>452.96408880000001</v>
+        <v>447.20241480000004</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="1"/>
-        <v>462.02337057600005</v>
+        <v>456.14646309599999</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="1"/>
-        <v>471.26383798752005</v>
+        <v>465.26939235791997</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" si="1"/>
-        <v>480.68911474727048</v>
+        <v>474.57478020507835</v>
       </c>
       <c r="X4" s="5">
         <f t="shared" si="1"/>
-        <v>490.30289704221587</v>
+        <v>484.0662758091799</v>
       </c>
       <c r="Y4" s="5">
         <f t="shared" si="1"/>
-        <v>500.10895498306019</v>
+        <v>493.74760132536352</v>
       </c>
       <c r="Z4" s="5">
         <f t="shared" si="1"/>
-        <v>510.11113408272143</v>
+        <v>503.62255335187081</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="1"/>
-        <v>520.31335676437584</v>
+        <v>513.69500441890818</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>530.71962389966336</v>
+        <v>523.96890450728642</v>
       </c>
     </row>
     <row r="5" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1102,7 +1112,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:H5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:I5" si="2">C3-C4</f>
         <v>65.5</v>
       </c>
       <c r="D5" s="8">
@@ -1126,12 +1136,12 @@
         <v>71.7</v>
       </c>
       <c r="I5" s="8">
-        <f>I3*0.41</f>
-        <v>77.899999999999991</v>
+        <f t="shared" si="2"/>
+        <v>73.800000000000011</v>
       </c>
       <c r="J5" s="8">
         <f>J3*0.39</f>
-        <v>82.718999999999994</v>
+        <v>81.081000000000003</v>
       </c>
       <c r="L5" s="8">
         <f t="shared" ref="L5:R5" si="3">L3-L4</f>
@@ -1159,47 +1169,47 @@
       </c>
       <c r="R5" s="8">
         <f t="shared" si="3"/>
-        <v>303.91899999999998</v>
+        <v>298.18099999999998</v>
       </c>
       <c r="S5" s="8">
         <f>S3*0.42</f>
-        <v>327.21863999999999</v>
+        <v>323.05644000000001</v>
       </c>
       <c r="T5" s="8">
         <f>T3*0.43</f>
-        <v>341.70975120000003</v>
+        <v>337.36322519999999</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" ref="U5:AB5" si="4">U3*0.43</f>
-        <v>348.54394622400002</v>
+        <v>344.11048970400003</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="4"/>
-        <v>355.51482514848004</v>
+        <v>350.99269949808001</v>
       </c>
       <c r="W5" s="8">
         <f t="shared" si="4"/>
-        <v>362.62512165144966</v>
+        <v>358.01255348804159</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" si="4"/>
-        <v>369.87762408447867</v>
+        <v>365.17280455780241</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="4"/>
-        <v>377.27517656616823</v>
+        <v>372.47626064895843</v>
       </c>
       <c r="Z5" s="8">
         <f t="shared" si="4"/>
-        <v>384.82068009749156</v>
+        <v>379.92578586193758</v>
       </c>
       <c r="AA5" s="8">
         <f t="shared" si="4"/>
-        <v>392.51709369944138</v>
+        <v>387.52430157917638</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="4"/>
-        <v>400.36743557343027</v>
+        <v>395.27478761075992</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.3">
@@ -1226,8 +1236,7 @@
         <v>31.7</v>
       </c>
       <c r="I6" s="5">
-        <f>E6*1.1</f>
-        <v>33.22</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5">
         <f>F6*1.07</f>
@@ -1253,47 +1262,47 @@
       </c>
       <c r="R6" s="5">
         <f t="shared" ref="R6:R8" si="6">SUM(G6:J6)</f>
-        <v>129.11799999999999</v>
+        <v>128.898</v>
       </c>
       <c r="S6" s="5">
         <f>R6*1.04</f>
-        <v>134.28272000000001</v>
+        <v>134.05392000000001</v>
       </c>
       <c r="T6" s="5">
         <f>S6*1.03</f>
-        <v>138.3112016</v>
+        <v>138.07553760000002</v>
       </c>
       <c r="U6" s="5">
         <f>T6*1.02</f>
-        <v>141.077425632</v>
+        <v>140.83704835200001</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" ref="V6:W6" si="7">U6*1.02</f>
-        <v>143.89897414463999</v>
+        <v>143.65378931904002</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="7"/>
-        <v>146.77695362753281</v>
+        <v>146.52686510542082</v>
       </c>
       <c r="X6" s="5">
         <f>W6*1.01</f>
-        <v>148.24472316380815</v>
+        <v>147.99213375647503</v>
       </c>
       <c r="Y6" s="5">
         <f t="shared" ref="Y6:AB6" si="8">X6*1.01</f>
-        <v>149.72717039544622</v>
+        <v>149.47205509403977</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="8"/>
-        <v>151.22444209940068</v>
+        <v>150.96677564498017</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="8"/>
-        <v>152.73668652039467</v>
+        <v>152.47644340142998</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="8"/>
-        <v>154.26405338559863</v>
+        <v>154.00120783544426</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.3">
@@ -1320,12 +1329,11 @@
         <v>24.8</v>
       </c>
       <c r="I7" s="5">
-        <f>I3*0.14</f>
-        <v>26.6</v>
+        <v>24.7</v>
       </c>
       <c r="J7" s="5">
         <f>J3*0.13</f>
-        <v>27.573</v>
+        <v>27.027000000000001</v>
       </c>
       <c r="L7" s="5">
         <v>35</v>
@@ -1347,47 +1355,47 @@
       </c>
       <c r="R7" s="5">
         <f t="shared" si="6"/>
-        <v>105.47300000000001</v>
+        <v>103.027</v>
       </c>
       <c r="S7" s="5">
         <f>S3*0.13</f>
-        <v>101.28196</v>
+        <v>99.993660000000006</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" ref="T7:AB7" si="9">T3*0.13</f>
-        <v>103.30759920000001</v>
+        <v>101.9935332</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="9"/>
-        <v>105.37375118400001</v>
+        <v>104.03340386400001</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="9"/>
-        <v>107.48122620768001</v>
+        <v>106.11407194128</v>
       </c>
       <c r="W7" s="5">
         <f t="shared" si="9"/>
-        <v>109.63085073183362</v>
+        <v>108.2363533801056</v>
       </c>
       <c r="X7" s="5">
         <f t="shared" si="9"/>
-        <v>111.8234677464703</v>
+        <v>110.4010804477077</v>
       </c>
       <c r="Y7" s="5">
         <f t="shared" si="9"/>
-        <v>114.0599371013997</v>
+        <v>112.60910205666185</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="9"/>
-        <v>116.34113584342769</v>
+        <v>114.86128409779509</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="9"/>
-        <v>118.66795856029624</v>
+        <v>117.158509779751</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="9"/>
-        <v>121.04131773150218</v>
+        <v>119.50167997534602</v>
       </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.3">
@@ -1414,8 +1422,7 @@
         <v>18.8</v>
       </c>
       <c r="I8" s="5">
-        <f>E8*1.1</f>
-        <v>19.360000000000003</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="J8" s="5">
         <f>F8*1.05</f>
@@ -1441,47 +1448,47 @@
       </c>
       <c r="R8" s="5">
         <f t="shared" si="6"/>
-        <v>77.84</v>
+        <v>76.580000000000013</v>
       </c>
       <c r="S8" s="5">
         <f>R8*1.05</f>
-        <v>81.732000000000014</v>
+        <v>80.40900000000002</v>
       </c>
       <c r="T8" s="5">
         <f>S8*1.04</f>
-        <v>85.001280000000023</v>
+        <v>83.625360000000029</v>
       </c>
       <c r="U8" s="5">
         <f>T8*1.02</f>
-        <v>86.701305600000026</v>
+        <v>85.297867200000027</v>
       </c>
       <c r="V8" s="5">
         <f>U8*1.02</f>
-        <v>88.435331712000021</v>
+        <v>87.003824544000025</v>
       </c>
       <c r="W8" s="5">
         <f>V8*1.01</f>
-        <v>89.319685029120024</v>
+        <v>87.873862789440025</v>
       </c>
       <c r="X8" s="5">
         <f t="shared" ref="X8:AB8" si="10">W8*1.01</f>
-        <v>90.212881879411228</v>
+        <v>88.752601417334432</v>
       </c>
       <c r="Y8" s="5">
         <f t="shared" si="10"/>
-        <v>91.115010698205339</v>
+        <v>89.640127431507779</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="10"/>
-        <v>92.026160805187388</v>
+        <v>90.53652870582286</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="10"/>
-        <v>92.946422413239262</v>
+        <v>91.441893992881091</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="10"/>
-        <v>93.87588663737165</v>
+        <v>92.3563129328099</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.3">
@@ -1514,11 +1521,11 @@
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9:J9" si="12">SUM(I6:I8)</f>
-        <v>79.180000000000007</v>
+        <v>75.800000000000011</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="12"/>
-        <v>81.751000000000005</v>
+        <v>81.204999999999998</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" ref="L9:R9" si="13">SUM(L6:L8)</f>
@@ -1546,47 +1553,47 @@
       </c>
       <c r="R9" s="5">
         <f t="shared" si="13"/>
-        <v>312.43100000000004</v>
+        <v>308.505</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" ref="S9:AB9" si="14">SUM(S6:S8)</f>
-        <v>317.29668000000004</v>
+        <v>314.45658000000003</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="14"/>
-        <v>326.62008080000004</v>
+        <v>323.69443080000008</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="14"/>
-        <v>333.15248241600005</v>
+        <v>330.16831941600003</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="14"/>
-        <v>339.81553206432</v>
+        <v>336.77168580432004</v>
       </c>
       <c r="W9" s="5">
         <f t="shared" si="14"/>
-        <v>345.72748938848645</v>
+        <v>342.63708127496642</v>
       </c>
       <c r="X9" s="5">
         <f t="shared" si="14"/>
-        <v>350.28107278968963</v>
+        <v>347.14581562151716</v>
       </c>
       <c r="Y9" s="5">
         <f t="shared" si="14"/>
-        <v>354.90211819505123</v>
+        <v>351.72128458220942</v>
       </c>
       <c r="Z9" s="5">
         <f t="shared" si="14"/>
-        <v>359.59173874801576</v>
+        <v>356.36458844859817</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="14"/>
-        <v>364.35106749393015</v>
+        <v>361.0768471740621</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="14"/>
-        <v>369.18125775447243</v>
+        <v>365.85920074360018</v>
       </c>
     </row>
     <row r="10" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1619,11 +1626,11 @@
       </c>
       <c r="I10" s="8">
         <f t="shared" ref="I10:J10" si="16">I5-I9</f>
-        <v>-1.2800000000000153</v>
+        <v>-2</v>
       </c>
       <c r="J10" s="8">
         <f t="shared" si="16"/>
-        <v>0.96799999999998931</v>
+        <v>-0.12399999999999523</v>
       </c>
       <c r="L10" s="8">
         <f t="shared" ref="L10:R10" si="17">L5-L9</f>
@@ -1651,47 +1658,47 @@
       </c>
       <c r="R10" s="8">
         <f t="shared" si="17"/>
-        <v>-8.5120000000000573</v>
+        <v>-10.324000000000012</v>
       </c>
       <c r="S10" s="8">
         <f>S5-S9+S35+S36</f>
-        <v>65.174759999999964</v>
+        <v>63.852659999999979</v>
       </c>
       <c r="T10" s="8">
         <f t="shared" ref="T10:AB10" si="18">T5-T9+T35+T36</f>
-        <v>71.997498399999984</v>
+        <v>70.576622399999906</v>
       </c>
       <c r="U10" s="8">
         <f t="shared" si="18"/>
-        <v>73.632770087999972</v>
+        <v>72.183476568000003</v>
       </c>
       <c r="V10" s="8">
         <f t="shared" si="18"/>
-        <v>74.916678426960047</v>
+        <v>73.438399036559971</v>
       </c>
       <c r="W10" s="8">
         <f t="shared" si="18"/>
-        <v>77.108730779191205</v>
+        <v>75.586570729303162</v>
       </c>
       <c r="X10" s="8">
         <f t="shared" si="18"/>
-        <v>80.409760796179313</v>
+        <v>78.840198437675525</v>
       </c>
       <c r="Y10" s="8">
         <f t="shared" si="18"/>
-        <v>83.794399967521187</v>
+        <v>82.176317663153199</v>
       </c>
       <c r="Z10" s="8">
         <f t="shared" si="18"/>
-        <v>87.264496361844039</v>
+        <v>85.596752425707649</v>
       </c>
       <c r="AA10" s="8">
         <f t="shared" si="18"/>
-        <v>90.821936768003127</v>
+        <v>89.103364967606183</v>
       </c>
       <c r="AB10" s="8">
         <f t="shared" si="18"/>
-        <v>94.468647487074691</v>
+        <v>92.698056535276578</v>
       </c>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.3">
@@ -1801,7 +1808,7 @@
         <v>0.5</v>
       </c>
       <c r="I12" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="5">
         <v>1</v>
@@ -1826,47 +1833,47 @@
       </c>
       <c r="R12" s="5">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S12" s="5">
         <f>R12*1.05</f>
-        <v>3.1500000000000004</v>
+        <v>2.625</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" ref="T12:AB12" si="21">S12*1.05</f>
-        <v>3.3075000000000006</v>
+        <v>2.7562500000000001</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="21"/>
-        <v>3.4728750000000006</v>
+        <v>2.8940625000000004</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="21"/>
-        <v>3.6465187500000007</v>
+        <v>3.0387656250000004</v>
       </c>
       <c r="W12" s="5">
         <f t="shared" si="21"/>
-        <v>3.8288446875000011</v>
+        <v>3.1907039062500004</v>
       </c>
       <c r="X12" s="5">
         <f t="shared" si="21"/>
-        <v>4.0202869218750017</v>
+        <v>3.3502391015625008</v>
       </c>
       <c r="Y12" s="5">
         <f t="shared" si="21"/>
-        <v>4.2213012679687516</v>
+        <v>3.517751056640626</v>
       </c>
       <c r="Z12" s="5">
         <f t="shared" si="21"/>
-        <v>4.4323663313671897</v>
+        <v>3.6936386094726577</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="21"/>
-        <v>4.6539846479355491</v>
+        <v>3.8783205399462908</v>
       </c>
       <c r="AB12" s="5">
         <f t="shared" si="21"/>
-        <v>4.8866838803323267</v>
+        <v>4.0722365669436051</v>
       </c>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.3">
@@ -1981,7 +1988,7 @@
       </c>
       <c r="I14" s="5">
         <f t="shared" ref="I14:J14" si="23">SUM(I11:I13)</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" si="23"/>
@@ -2013,47 +2020,47 @@
       </c>
       <c r="R14" s="5">
         <f t="shared" si="24"/>
-        <v>4.0999999999999996</v>
+        <v>3.6</v>
       </c>
       <c r="S14" s="5">
         <f t="shared" si="24"/>
-        <v>3.1500000000000004</v>
+        <v>2.625</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" ref="T14:AB14" si="25">SUM(T11:T13)</f>
-        <v>3.3075000000000006</v>
+        <v>2.7562500000000001</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="25"/>
-        <v>3.4728750000000006</v>
+        <v>2.8940625000000004</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="25"/>
-        <v>3.6465187500000007</v>
+        <v>3.0387656250000004</v>
       </c>
       <c r="W14" s="5">
         <f t="shared" si="25"/>
-        <v>3.8288446875000011</v>
+        <v>3.1907039062500004</v>
       </c>
       <c r="X14" s="5">
         <f t="shared" si="25"/>
-        <v>4.0202869218750017</v>
+        <v>3.3502391015625008</v>
       </c>
       <c r="Y14" s="5">
         <f t="shared" si="25"/>
-        <v>4.2213012679687516</v>
+        <v>3.517751056640626</v>
       </c>
       <c r="Z14" s="5">
         <f t="shared" si="25"/>
-        <v>4.4323663313671897</v>
+        <v>3.6936386094726577</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="25"/>
-        <v>4.6539846479355491</v>
+        <v>3.8783205399462908</v>
       </c>
       <c r="AB14" s="5">
         <f t="shared" si="25"/>
-        <v>4.8866838803323267</v>
+        <v>4.0722365669436051</v>
       </c>
     </row>
     <row r="15" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2086,11 +2093,11 @@
       </c>
       <c r="I15" s="8">
         <f t="shared" ref="I15:J15" si="27">I10-I14</f>
-        <v>-3.2800000000000153</v>
+        <v>-3.5</v>
       </c>
       <c r="J15" s="8">
         <f t="shared" si="27"/>
-        <v>-1.0320000000000107</v>
+        <v>-2.1239999999999952</v>
       </c>
       <c r="L15" s="8">
         <f t="shared" ref="L15:S15" si="28">L10-L14</f>
@@ -2118,47 +2125,47 @@
       </c>
       <c r="R15" s="8">
         <f t="shared" si="28"/>
-        <v>-12.612000000000057</v>
+        <v>-13.924000000000012</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="28"/>
-        <v>62.024759999999965</v>
+        <v>61.227659999999979</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" ref="T15:AB15" si="29">T10-T14</f>
-        <v>68.689998399999979</v>
+        <v>67.820372399999911</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="29"/>
-        <v>70.159895087999971</v>
+        <v>69.289414067999999</v>
       </c>
       <c r="V15" s="8">
         <f t="shared" si="29"/>
-        <v>71.270159676960049</v>
+        <v>70.399633411559975</v>
       </c>
       <c r="W15" s="8">
         <f t="shared" si="29"/>
-        <v>73.27988609169121</v>
+        <v>72.395866823053154</v>
       </c>
       <c r="X15" s="8">
         <f t="shared" si="29"/>
-        <v>76.389473874304315</v>
+        <v>75.489959336113031</v>
       </c>
       <c r="Y15" s="8">
         <f t="shared" si="29"/>
-        <v>79.573098699552432</v>
+        <v>78.658566606512579</v>
       </c>
       <c r="Z15" s="8">
         <f t="shared" si="29"/>
-        <v>82.832130030476847</v>
+        <v>81.903113816234992</v>
       </c>
       <c r="AA15" s="8">
         <f t="shared" si="29"/>
-        <v>86.167952120067582</v>
+        <v>85.225044427659896</v>
       </c>
       <c r="AB15" s="8">
         <f t="shared" si="29"/>
-        <v>89.581963606742363</v>
+        <v>88.625819968332976</v>
       </c>
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.3">
@@ -2185,7 +2192,7 @@
         <v>0.1</v>
       </c>
       <c r="I16" s="5">
-        <v>0</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="J16" s="5">
         <v>0</v>
@@ -2210,7 +2217,7 @@
       </c>
       <c r="R16" s="5">
         <f>SUM(G16:J16)</f>
-        <v>0.2</v>
+        <v>-2.0999999999999996</v>
       </c>
       <c r="S16" s="5">
         <v>0</v>
@@ -2273,11 +2280,11 @@
       </c>
       <c r="I17" s="8">
         <f t="shared" ref="I17:J17" si="31">I15-I16</f>
-        <v>-3.2800000000000153</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="J17" s="8">
         <f t="shared" si="31"/>
-        <v>-1.0320000000000107</v>
+        <v>-2.1239999999999952</v>
       </c>
       <c r="L17" s="8">
         <f t="shared" ref="L17:S17" si="32">L15-L16</f>
@@ -2305,499 +2312,499 @@
       </c>
       <c r="R17" s="8">
         <f t="shared" si="32"/>
-        <v>-12.812000000000056</v>
+        <v>-11.824000000000012</v>
       </c>
       <c r="S17" s="8">
         <f t="shared" si="32"/>
-        <v>62.024759999999965</v>
+        <v>61.227659999999979</v>
       </c>
       <c r="T17" s="8">
         <f t="shared" ref="T17:AB17" si="33">T15-T16</f>
-        <v>68.689998399999979</v>
+        <v>67.820372399999911</v>
       </c>
       <c r="U17" s="8">
         <f t="shared" si="33"/>
-        <v>70.159895087999971</v>
+        <v>69.289414067999999</v>
       </c>
       <c r="V17" s="8">
         <f t="shared" si="33"/>
-        <v>71.270159676960049</v>
+        <v>70.399633411559975</v>
       </c>
       <c r="W17" s="8">
         <f t="shared" si="33"/>
-        <v>73.27988609169121</v>
+        <v>72.395866823053154</v>
       </c>
       <c r="X17" s="8">
         <f t="shared" si="33"/>
-        <v>76.389473874304315</v>
+        <v>75.489959336113031</v>
       </c>
       <c r="Y17" s="8">
         <f t="shared" si="33"/>
-        <v>79.573098699552432</v>
+        <v>78.658566606512579</v>
       </c>
       <c r="Z17" s="8">
         <f t="shared" si="33"/>
-        <v>82.832130030476847</v>
+        <v>81.903113816234992</v>
       </c>
       <c r="AA17" s="8">
         <f t="shared" si="33"/>
-        <v>86.167952120067582</v>
+        <v>85.225044427659896</v>
       </c>
       <c r="AB17" s="8">
         <f t="shared" si="33"/>
-        <v>89.581963606742363</v>
+        <v>88.625819968332976</v>
       </c>
       <c r="AC17" s="1">
         <f>AB17*(1+$AE$22)</f>
-        <v>88.686143970674934</v>
+        <v>87.739561768649651</v>
       </c>
       <c r="AD17" s="1">
         <f t="shared" ref="AD17:CO17" si="34">AC17*(1+$AE$22)</f>
-        <v>87.799282530968185</v>
+        <v>86.862166150963148</v>
       </c>
       <c r="AE17" s="1">
         <f t="shared" si="34"/>
-        <v>86.921289705658509</v>
+        <v>85.993544489453512</v>
       </c>
       <c r="AF17" s="1">
         <f t="shared" si="34"/>
-        <v>86.052076808601925</v>
+        <v>85.13360904455898</v>
       </c>
       <c r="AG17" s="1">
         <f t="shared" si="34"/>
-        <v>85.191556040515906</v>
+        <v>84.282272954113395</v>
       </c>
       <c r="AH17" s="1">
         <f t="shared" si="34"/>
-        <v>84.339640480110745</v>
+        <v>83.439450224572255</v>
       </c>
       <c r="AI17" s="1">
         <f t="shared" si="34"/>
-        <v>83.496244075309633</v>
+        <v>82.605055722326526</v>
       </c>
       <c r="AJ17" s="1">
         <f t="shared" si="34"/>
-        <v>82.661281634556531</v>
+        <v>81.779005165103257</v>
       </c>
       <c r="AK17" s="1">
         <f t="shared" si="34"/>
-        <v>81.834668818210972</v>
+        <v>80.961215113452226</v>
       </c>
       <c r="AL17" s="1">
         <f t="shared" si="34"/>
-        <v>81.016322130028854</v>
+        <v>80.15160296231771</v>
       </c>
       <c r="AM17" s="1">
         <f t="shared" si="34"/>
-        <v>80.206158908728568</v>
+        <v>79.350086932694538</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="34"/>
-        <v>79.404097319641281</v>
+        <v>78.55658606336759</v>
       </c>
       <c r="AO17" s="1">
         <f t="shared" si="34"/>
-        <v>78.610056346444864</v>
+        <v>77.771020202733908</v>
       </c>
       <c r="AP17" s="1">
         <f t="shared" si="34"/>
-        <v>77.82395578298042</v>
+        <v>76.993310000706572</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="34"/>
-        <v>77.045716225150613</v>
+        <v>76.223376900699506</v>
       </c>
       <c r="AR17" s="1">
         <f t="shared" si="34"/>
-        <v>76.27525906289911</v>
+        <v>75.461143131692509</v>
       </c>
       <c r="AS17" s="1">
         <f t="shared" si="34"/>
-        <v>75.512506472270118</v>
+        <v>74.706531700375578</v>
       </c>
       <c r="AT17" s="1">
         <f t="shared" si="34"/>
-        <v>74.757381407547413</v>
+        <v>73.959466383371819</v>
       </c>
       <c r="AU17" s="1">
         <f t="shared" si="34"/>
-        <v>74.009807593471933</v>
+        <v>73.219871719538105</v>
       </c>
       <c r="AV17" s="1">
         <f t="shared" si="34"/>
-        <v>73.269709517537208</v>
+        <v>72.487673002342717</v>
       </c>
       <c r="AW17" s="1">
         <f t="shared" si="34"/>
-        <v>72.53701242236184</v>
+        <v>71.762796272319292</v>
       </c>
       <c r="AX17" s="1">
         <f t="shared" si="34"/>
-        <v>71.811642298138224</v>
+        <v>71.045168309596093</v>
       </c>
       <c r="AY17" s="1">
         <f t="shared" si="34"/>
-        <v>71.093525875156843</v>
+        <v>70.334716626500125</v>
       </c>
       <c r="AZ17" s="1">
         <f t="shared" si="34"/>
-        <v>70.382590616405267</v>
+        <v>69.631369460235121</v>
       </c>
       <c r="BA17" s="1">
         <f t="shared" si="34"/>
-        <v>69.678764710241211</v>
+        <v>68.935055765632768</v>
       </c>
       <c r="BB17" s="1">
         <f t="shared" si="34"/>
-        <v>68.9819770631388</v>
+        <v>68.245705207976442</v>
       </c>
       <c r="BC17" s="1">
         <f t="shared" si="34"/>
-        <v>68.292157292507412</v>
+        <v>67.563248155896673</v>
       </c>
       <c r="BD17" s="1">
         <f t="shared" si="34"/>
-        <v>67.609235719582344</v>
+        <v>66.887615674337709</v>
       </c>
       <c r="BE17" s="1">
         <f t="shared" si="34"/>
-        <v>66.933143362386517</v>
+        <v>66.218739517594329</v>
       </c>
       <c r="BF17" s="1">
         <f t="shared" si="34"/>
-        <v>66.263811928762649</v>
+        <v>65.556552122418381</v>
       </c>
       <c r="BG17" s="1">
         <f t="shared" si="34"/>
-        <v>65.601173809475029</v>
+        <v>64.900986601194191</v>
       </c>
       <c r="BH17" s="1">
         <f t="shared" si="34"/>
-        <v>64.945162071380281</v>
+        <v>64.251976735182254</v>
       </c>
       <c r="BI17" s="1">
         <f t="shared" si="34"/>
-        <v>64.295710450666476</v>
+        <v>63.609456967830432</v>
       </c>
       <c r="BJ17" s="1">
         <f t="shared" si="34"/>
-        <v>63.652753346159813</v>
+        <v>62.973362398152126</v>
       </c>
       <c r="BK17" s="1">
         <f t="shared" si="34"/>
-        <v>63.016225812698217</v>
+        <v>62.343628774170604</v>
       </c>
       <c r="BL17" s="1">
         <f t="shared" si="34"/>
-        <v>62.386063554571237</v>
+        <v>61.7201924864289</v>
       </c>
       <c r="BM17" s="1">
         <f t="shared" si="34"/>
-        <v>61.762202919025526</v>
+        <v>61.10299056156461</v>
       </c>
       <c r="BN17" s="1">
         <f t="shared" si="34"/>
-        <v>61.144580889835268</v>
+        <v>60.491960655948965</v>
       </c>
       <c r="BO17" s="1">
         <f t="shared" si="34"/>
-        <v>60.533135080936916</v>
+        <v>59.887041049389474</v>
       </c>
       <c r="BP17" s="1">
         <f t="shared" si="34"/>
-        <v>59.927803730127543</v>
+        <v>59.288170638895579</v>
       </c>
       <c r="BQ17" s="1">
         <f t="shared" si="34"/>
-        <v>59.328525692826268</v>
+        <v>58.695288932506621</v>
       </c>
       <c r="BR17" s="1">
         <f t="shared" si="34"/>
-        <v>58.735240435898007</v>
+        <v>58.108336043181552</v>
       </c>
       <c r="BS17" s="1">
         <f t="shared" si="34"/>
-        <v>58.147888031539026</v>
+        <v>57.527252682749733</v>
       </c>
       <c r="BT17" s="1">
         <f t="shared" si="34"/>
-        <v>57.566409151223638</v>
+        <v>56.951980155922236</v>
       </c>
       <c r="BU17" s="1">
         <f t="shared" si="34"/>
-        <v>56.990745059711401</v>
+        <v>56.382460354363012</v>
       </c>
       <c r="BV17" s="1">
         <f t="shared" si="34"/>
-        <v>56.420837609114287</v>
+        <v>55.818635750819382</v>
       </c>
       <c r="BW17" s="1">
         <f t="shared" si="34"/>
-        <v>55.856629233023142</v>
+        <v>55.260449393311191</v>
       </c>
       <c r="BX17" s="1">
         <f t="shared" si="34"/>
-        <v>55.298062940692908</v>
+        <v>54.707844899378081</v>
       </c>
       <c r="BY17" s="1">
         <f t="shared" si="34"/>
-        <v>54.745082311285977</v>
+        <v>54.160766450384301</v>
       </c>
       <c r="BZ17" s="1">
         <f t="shared" si="34"/>
-        <v>54.197631488173116</v>
+        <v>53.619158785880458</v>
       </c>
       <c r="CA17" s="1">
         <f t="shared" si="34"/>
-        <v>53.655655173291386</v>
+        <v>53.082967198021656</v>
       </c>
       <c r="CB17" s="1">
         <f t="shared" si="34"/>
-        <v>53.119098621558472</v>
+        <v>52.552137526041442</v>
       </c>
       <c r="CC17" s="1">
         <f t="shared" si="34"/>
-        <v>52.587907635342887</v>
+        <v>52.026616150781024</v>
       </c>
       <c r="CD17" s="1">
         <f t="shared" si="34"/>
-        <v>52.062028558989461</v>
+        <v>51.506349989273211</v>
       </c>
       <c r="CE17" s="1">
         <f t="shared" si="34"/>
-        <v>51.541408273399568</v>
+        <v>50.991286489380478</v>
       </c>
       <c r="CF17" s="1">
         <f t="shared" si="34"/>
-        <v>51.025994190665571</v>
+        <v>50.481373624486672</v>
       </c>
       <c r="CG17" s="1">
         <f t="shared" si="34"/>
-        <v>50.515734248758918</v>
+        <v>49.976559888241802</v>
       </c>
       <c r="CH17" s="1">
         <f t="shared" si="34"/>
-        <v>50.010576906271325</v>
+        <v>49.476794289359383</v>
       </c>
       <c r="CI17" s="1">
         <f t="shared" si="34"/>
-        <v>49.510471137208611</v>
+        <v>48.982026346465787</v>
       </c>
       <c r="CJ17" s="1">
         <f t="shared" si="34"/>
-        <v>49.015366425836525</v>
+        <v>48.492206083001129</v>
       </c>
       <c r="CK17" s="1">
         <f t="shared" si="34"/>
-        <v>48.52521276157816</v>
+        <v>48.00728402217112</v>
       </c>
       <c r="CL17" s="1">
         <f t="shared" si="34"/>
-        <v>48.03996063396238</v>
+        <v>47.527211181949411</v>
       </c>
       <c r="CM17" s="1">
         <f t="shared" si="34"/>
-        <v>47.559561027622756</v>
+        <v>47.051939070129919</v>
       </c>
       <c r="CN17" s="1">
         <f t="shared" si="34"/>
-        <v>47.083965417346526</v>
+        <v>46.58141967942862</v>
       </c>
       <c r="CO17" s="1">
         <f t="shared" si="34"/>
-        <v>46.613125763173059</v>
+        <v>46.115605482634336</v>
       </c>
       <c r="CP17" s="1">
         <f t="shared" ref="CP17:EK17" si="35">CO17*(1+$AE$22)</f>
-        <v>46.146994505541329</v>
+        <v>45.65444942780799</v>
       </c>
       <c r="CQ17" s="1">
         <f t="shared" si="35"/>
-        <v>45.685524560485916</v>
+        <v>45.197904933529912</v>
       </c>
       <c r="CR17" s="1">
         <f t="shared" si="35"/>
-        <v>45.22866931488106</v>
+        <v>44.745925884194612</v>
       </c>
       <c r="CS17" s="1">
         <f t="shared" si="35"/>
-        <v>44.776382621732246</v>
+        <v>44.298466625352667</v>
       </c>
       <c r="CT17" s="1">
         <f t="shared" si="35"/>
-        <v>44.32861879551492</v>
+        <v>43.855481959099137</v>
       </c>
       <c r="CU17" s="1">
         <f t="shared" si="35"/>
-        <v>43.885332607559768</v>
+        <v>43.416927139508147</v>
       </c>
       <c r="CV17" s="1">
         <f t="shared" si="35"/>
-        <v>43.446479281484173</v>
+        <v>42.982757868113062</v>
       </c>
       <c r="CW17" s="1">
         <f t="shared" si="35"/>
-        <v>43.01201448866933</v>
+        <v>42.552930289431927</v>
       </c>
       <c r="CX17" s="1">
         <f t="shared" si="35"/>
-        <v>42.581894343782636</v>
+        <v>42.127400986537609</v>
       </c>
       <c r="CY17" s="1">
         <f t="shared" si="35"/>
-        <v>42.156075400344811</v>
+        <v>41.70612697667223</v>
       </c>
       <c r="CZ17" s="1">
         <f t="shared" si="35"/>
-        <v>41.73451464634136</v>
+        <v>41.289065706905511</v>
       </c>
       <c r="DA17" s="1">
         <f t="shared" si="35"/>
-        <v>41.317169499877949</v>
+        <v>40.876175049836455</v>
       </c>
       <c r="DB17" s="1">
         <f t="shared" si="35"/>
-        <v>40.903997804879168</v>
+        <v>40.467413299338091</v>
       </c>
       <c r="DC17" s="1">
         <f t="shared" si="35"/>
-        <v>40.49495782683038</v>
+        <v>40.062739166344713</v>
       </c>
       <c r="DD17" s="1">
         <f t="shared" si="35"/>
-        <v>40.090008248562079</v>
+        <v>39.662111774681264</v>
       </c>
       <c r="DE17" s="1">
         <f t="shared" si="35"/>
-        <v>39.689108166076458</v>
+        <v>39.265490656934453</v>
       </c>
       <c r="DF17" s="1">
         <f t="shared" si="35"/>
-        <v>39.292217084415697</v>
+        <v>38.872835750365105</v>
       </c>
       <c r="DG17" s="1">
         <f t="shared" si="35"/>
-        <v>38.899294913571538</v>
+        <v>38.484107392861453</v>
       </c>
       <c r="DH17" s="1">
         <f t="shared" si="35"/>
-        <v>38.510301964435826</v>
+        <v>38.099266318932841</v>
       </c>
       <c r="DI17" s="1">
         <f t="shared" si="35"/>
-        <v>38.125198944791464</v>
+        <v>37.718273655743509</v>
       </c>
       <c r="DJ17" s="1">
         <f t="shared" si="35"/>
-        <v>37.743946955343546</v>
+        <v>37.341090919186072</v>
       </c>
       <c r="DK17" s="1">
         <f t="shared" si="35"/>
-        <v>37.366507485790109</v>
+        <v>36.967680009994211</v>
       </c>
       <c r="DL17" s="1">
         <f t="shared" si="35"/>
-        <v>36.992842410932205</v>
+        <v>36.598003209894266</v>
       </c>
       <c r="DM17" s="1">
         <f t="shared" si="35"/>
-        <v>36.62291398682288</v>
+        <v>36.23202317779532</v>
       </c>
       <c r="DN17" s="1">
         <f t="shared" si="35"/>
-        <v>36.256684846954649</v>
+        <v>35.86970294601737</v>
       </c>
       <c r="DO17" s="1">
         <f t="shared" si="35"/>
-        <v>35.8941179984851</v>
+        <v>35.511005916557195</v>
       </c>
       <c r="DP17" s="1">
         <f t="shared" si="35"/>
-        <v>35.535176818500247</v>
+        <v>35.15589585739162</v>
       </c>
       <c r="DQ17" s="1">
         <f t="shared" si="35"/>
-        <v>35.179825050315245</v>
+        <v>34.804336898817702</v>
       </c>
       <c r="DR17" s="1">
         <f t="shared" si="35"/>
-        <v>34.828026799812093</v>
+        <v>34.456293529829523</v>
       </c>
       <c r="DS17" s="1">
         <f t="shared" si="35"/>
-        <v>34.479746531813973</v>
+        <v>34.111730594531224</v>
       </c>
       <c r="DT17" s="1">
         <f t="shared" si="35"/>
-        <v>34.134949066495835</v>
+        <v>33.770613288585913</v>
       </c>
       <c r="DU17" s="1">
         <f t="shared" si="35"/>
-        <v>33.793599575830875</v>
+        <v>33.432907155700057</v>
       </c>
       <c r="DV17" s="1">
         <f t="shared" si="35"/>
-        <v>33.455663580072567</v>
+        <v>33.098578084143057</v>
       </c>
       <c r="DW17" s="1">
         <f t="shared" si="35"/>
-        <v>33.121106944271844</v>
+        <v>32.767592303301626</v>
       </c>
       <c r="DX17" s="1">
         <f t="shared" si="35"/>
-        <v>32.789895874829128</v>
+        <v>32.439916380268606</v>
       </c>
       <c r="DY17" s="1">
         <f t="shared" si="35"/>
-        <v>32.461996916080835</v>
+        <v>32.115517216465918</v>
       </c>
       <c r="DZ17" s="1">
         <f t="shared" si="35"/>
-        <v>32.137376946920028</v>
+        <v>31.794362044301259</v>
       </c>
       <c r="EA17" s="1">
         <f t="shared" si="35"/>
-        <v>31.816003177450828</v>
+        <v>31.476418423858245</v>
       </c>
       <c r="EB17" s="1">
         <f t="shared" si="35"/>
-        <v>31.49784314567632</v>
+        <v>31.161654239619661</v>
       </c>
       <c r="EC17" s="1">
         <f t="shared" si="35"/>
-        <v>31.182864714219559</v>
+        <v>30.850037697223463</v>
       </c>
       <c r="ED17" s="1">
         <f t="shared" si="35"/>
-        <v>30.871036067077362</v>
+        <v>30.54153732025123</v>
       </c>
       <c r="EE17" s="1">
         <f t="shared" si="35"/>
-        <v>30.56232570640659</v>
+        <v>30.236121947048716</v>
       </c>
       <c r="EF17" s="1">
         <f t="shared" si="35"/>
-        <v>30.256702449342523</v>
+        <v>29.933760727578228</v>
       </c>
       <c r="EG17" s="1">
         <f t="shared" si="35"/>
-        <v>29.954135424849099</v>
+        <v>29.634423120302447</v>
       </c>
       <c r="EH17" s="1">
         <f t="shared" si="35"/>
-        <v>29.654594070600609</v>
+        <v>29.338078889099421</v>
       </c>
       <c r="EI17" s="1">
         <f t="shared" si="35"/>
-        <v>29.358048129894602</v>
+        <v>29.044698100208425</v>
       </c>
       <c r="EJ17" s="1">
         <f t="shared" si="35"/>
-        <v>29.064467648595656</v>
+        <v>28.754251119206341</v>
       </c>
       <c r="EK17" s="1">
         <f t="shared" si="35"/>
-        <v>28.773822972109699</v>
+        <v>28.466708608014276</v>
       </c>
     </row>
     <row r="18" spans="2:141" x14ac:dyDescent="0.3">
@@ -2829,80 +2836,80 @@
         <v>28.1</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" ref="I18:J18" si="37">28.1</f>
+        <f>28.6+2</f>
+        <v>30.6</v>
+      </c>
+      <c r="J18" s="5">
+        <f>28.6+2</f>
+        <v>30.6</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" ref="L18:Q18" si="37">28.1</f>
         <v>28.1</v>
       </c>
-      <c r="J18" s="5">
+      <c r="M18" s="5">
         <f t="shared" si="37"/>
         <v>28.1</v>
       </c>
-      <c r="L18" s="5">
-        <f t="shared" ref="L18:S18" si="38">28.1</f>
+      <c r="N18" s="5">
+        <f t="shared" si="37"/>
         <v>28.1</v>
       </c>
-      <c r="M18" s="5">
-        <f t="shared" si="38"/>
+      <c r="O18" s="5">
+        <f t="shared" si="37"/>
         <v>28.1</v>
       </c>
-      <c r="N18" s="5">
-        <f t="shared" si="38"/>
+      <c r="P18" s="5">
+        <f t="shared" si="37"/>
         <v>28.1</v>
       </c>
-      <c r="O18" s="5">
-        <f t="shared" si="38"/>
+      <c r="Q18" s="5">
+        <f t="shared" si="37"/>
         <v>28.1</v>
       </c>
-      <c r="P18" s="5">
-        <f t="shared" si="38"/>
-        <v>28.1</v>
-      </c>
-      <c r="Q18" s="5">
-        <f t="shared" si="38"/>
-        <v>28.1</v>
-      </c>
       <c r="R18" s="5">
-        <f t="shared" si="38"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="S18" s="5">
-        <f t="shared" si="38"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:AB18" si="39">28.1</f>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="W18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="X18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="Y18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="Z18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
       <c r="AB18" s="5">
-        <f t="shared" si="39"/>
-        <v>28.1</v>
+        <f>28.6+2</f>
+        <v>30.6</v>
       </c>
     </row>
     <row r="19" spans="2:141" x14ac:dyDescent="0.3">
@@ -2910,104 +2917,104 @@
         <v>28</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:H19" si="40">C17/C18</f>
+        <f t="shared" ref="C19:H19" si="38">C17/C18</f>
         <v>-0.32384341637010666</v>
       </c>
       <c r="D19" s="7">
+        <f t="shared" si="38"/>
+        <v>0.14234875444839828</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="38"/>
+        <v>1.4234875444840159E-2</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="38"/>
+        <v>-6.4056939501779459E-2</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="38"/>
+        <v>-0.13523131672597843</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="38"/>
+        <v>-0.16725978647686809</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" ref="I19:J19" si="39">I17/I18</f>
+        <v>-3.921568627450981E-2</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="39"/>
+        <v>-6.9411764705882187E-2</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" ref="L19:S19" si="40">L17/L18</f>
+        <v>8.5409252669039024E-2</v>
+      </c>
+      <c r="M19" s="7">
         <f t="shared" si="40"/>
-        <v>0.14234875444839828</v>
-      </c>
-      <c r="E19" s="7">
+        <v>-1.5729537366548039</v>
+      </c>
+      <c r="N19" s="7">
         <f t="shared" si="40"/>
-        <v>1.4234875444840159E-2</v>
-      </c>
-      <c r="F19" s="7">
+        <v>-0.9786476868327405</v>
+      </c>
+      <c r="O19" s="7">
         <f t="shared" si="40"/>
-        <v>-6.4056939501779459E-2</v>
-      </c>
-      <c r="G19" s="7">
+        <v>0.70106761565836473</v>
+      </c>
+      <c r="P19" s="7">
         <f t="shared" si="40"/>
-        <v>-0.13523131672597843</v>
-      </c>
-      <c r="H19" s="7">
+        <v>-0.58362989323843495</v>
+      </c>
+      <c r="Q19" s="7">
         <f t="shared" si="40"/>
-        <v>-0.16725978647686809</v>
-      </c>
-      <c r="I19" s="7">
-        <f t="shared" ref="I19:J19" si="41">I17/I18</f>
-        <v>-0.11672597864768737</v>
-      </c>
-      <c r="J19" s="7">
+        <v>-0.23131672597864761</v>
+      </c>
+      <c r="R19" s="7">
+        <f t="shared" si="40"/>
+        <v>-0.38640522875817029</v>
+      </c>
+      <c r="S19" s="7">
+        <f t="shared" si="40"/>
+        <v>2.0009039215686268</v>
+      </c>
+      <c r="T19" s="7">
+        <f t="shared" ref="T19:AB19" si="41">T17/T18</f>
+        <v>2.2163520392156832</v>
+      </c>
+      <c r="U19" s="7">
         <f t="shared" si="41"/>
-        <v>-3.6725978647687209E-2</v>
-      </c>
-      <c r="L19" s="7">
-        <f t="shared" ref="L19:S19" si="42">L17/L18</f>
-        <v>8.5409252669039024E-2</v>
-      </c>
-      <c r="M19" s="7">
-        <f t="shared" si="42"/>
-        <v>-1.5729537366548039</v>
-      </c>
-      <c r="N19" s="7">
-        <f t="shared" si="42"/>
-        <v>-0.9786476868327405</v>
-      </c>
-      <c r="O19" s="7">
-        <f t="shared" si="42"/>
-        <v>0.70106761565836473</v>
-      </c>
-      <c r="P19" s="7">
-        <f t="shared" si="42"/>
-        <v>-0.58362989323843495</v>
-      </c>
-      <c r="Q19" s="7">
-        <f t="shared" si="42"/>
-        <v>-0.23131672597864761</v>
-      </c>
-      <c r="R19" s="7">
-        <f t="shared" si="42"/>
-        <v>-0.45594306049822264</v>
-      </c>
-      <c r="S19" s="7">
-        <f t="shared" si="42"/>
-        <v>2.2072868327402122</v>
-      </c>
-      <c r="T19" s="7">
-        <f t="shared" ref="T19:AB19" si="43">T17/T18</f>
-        <v>2.4444839288256217</v>
-      </c>
-      <c r="U19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.496793419501778</v>
+        <v>2.2643599368627449</v>
       </c>
       <c r="V19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.5363046148384356</v>
+        <f t="shared" si="41"/>
+        <v>2.300641614756862</v>
       </c>
       <c r="W19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.6078251278181925</v>
+        <f t="shared" si="41"/>
+        <v>2.3658780007533711</v>
       </c>
       <c r="X19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.7184866147439255</v>
+        <f t="shared" si="41"/>
+        <v>2.4669921351670925</v>
       </c>
       <c r="Y19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.831782871870193</v>
+        <f t="shared" si="41"/>
+        <v>2.5705413923696918</v>
       </c>
       <c r="Z19" s="7">
-        <f t="shared" si="43"/>
-        <v>2.9477626345365424</v>
+        <f t="shared" si="41"/>
+        <v>2.6765723469357838</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" si="43"/>
-        <v>3.0664751644152162</v>
+        <f t="shared" si="41"/>
+        <v>2.7851321708385584</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="43"/>
-        <v>3.1879702351153862</v>
+        <f t="shared" si="41"/>
+        <v>2.8962686264161102</v>
       </c>
     </row>
     <row r="21" spans="2:141" x14ac:dyDescent="0.3">
@@ -3025,16 +3032,16 @@
         <v>3.6866359447004671E-2</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" ref="I21:J21" si="44">I3/E3-1</f>
-        <v>-2.0113460546673623E-2</v>
+        <f t="shared" ref="I21:J21" si="42">I3/E3-1</f>
+        <v>-1.0314595152140282E-2</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="44"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="42"/>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9">
-        <f t="shared" ref="M21" si="45">M3/L3-1</f>
+        <f t="shared" ref="M21" si="43">M3/L3-1</f>
         <v>0.47506448839208959</v>
       </c>
       <c r="N21" s="9">
@@ -3055,46 +3062,46 @@
       </c>
       <c r="R21" s="9">
         <f>R3/Q3-1</f>
-        <v>1.05544422177688E-2</v>
+        <v>7.4816299265196839E-3</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:AB21" si="46">S3/R3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="S21:AB21" si="44">S3/R3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3103,43 +3110,43 @@
         <v>36</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:H22" si="47">C5/C3</f>
+        <f t="shared" ref="C22:H22" si="45">C5/C3</f>
         <v>0.38304093567251463</v>
       </c>
       <c r="D22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.37327188940092165</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.37751418256833419</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.36428571428571427</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.41078600114744696</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.39833333333333337</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" ref="I22:J22" si="46">I5/I3</f>
+        <v>0.38457529963522674</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="46"/>
+        <v>0.39</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" ref="L22:M22" si="47">L5/L3</f>
+        <v>0.46259673258813411</v>
+      </c>
+      <c r="M22" s="9">
         <f t="shared" si="47"/>
-        <v>0.37327188940092165</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.37751418256833419</v>
-      </c>
-      <c r="F22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.36428571428571427</v>
-      </c>
-      <c r="G22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.41078600114744696</v>
-      </c>
-      <c r="H22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.39833333333333337</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" ref="I22:J22" si="48">I5/I3</f>
-        <v>0.41</v>
-      </c>
-      <c r="J22" s="9">
-        <f t="shared" si="48"/>
-        <v>0.38999999999999996</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" ref="L22:M22" si="49">L5/L3</f>
-        <v>0.46259673258813411</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="49"/>
         <v>0.45992422034392305</v>
       </c>
       <c r="N22" s="9">
@@ -3160,46 +3167,46 @@
       </c>
       <c r="R22" s="9">
         <f>R5/R3</f>
-        <v>0.40179666842940243</v>
+        <v>0.39541307518896696</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:AB22" si="50">S5/S3</f>
+        <f t="shared" ref="S22:AB22" si="48">S5/S3</f>
         <v>0.42</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="48"/>
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
-      <c r="V22" s="9">
-        <f t="shared" si="50"/>
+      <c r="X22" s="9">
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
-      <c r="W22" s="9">
-        <f t="shared" si="50"/>
+      <c r="Y22" s="9">
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
-      <c r="X22" s="9">
-        <f t="shared" si="50"/>
+      <c r="Z22" s="9">
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="50"/>
+      <c r="AA22" s="9">
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="50"/>
-        <v>0.43</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="50"/>
-        <v>0.43</v>
-      </c>
       <c r="AB22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
       <c r="AD22" t="s">
@@ -3226,16 +3233,16 @@
         <v>0.12811387900355853</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23:J23" si="51">I6/E6-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="I23:J23" si="49">I6/E6-1</f>
+        <v>9.27152317880795E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="L23" s="9"/>
       <c r="M23" s="9">
-        <f t="shared" ref="M23" si="52">M6/L6-1</f>
+        <f t="shared" ref="M23" si="50">M6/L6-1</f>
         <v>0.33650793650793664</v>
       </c>
       <c r="N23" s="9">
@@ -3256,46 +3263,46 @@
       </c>
       <c r="R23" s="9">
         <f>R6/Q6-1</f>
-        <v>8.8684654300168697E-2</v>
+        <v>8.682967959527832E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:AB23" si="53">S6/R6-1</f>
+        <f t="shared" ref="S23:AB23" si="51">S6/R6-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD23" t="s">
@@ -3310,43 +3317,43 @@
         <v>38</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:H24" si="54">C7/C3</f>
+        <f t="shared" ref="C24:H24" si="52">C7/C3</f>
         <v>0.17017543859649123</v>
       </c>
       <c r="D24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.15034562211981567</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.13563692625064466</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.13428571428571429</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.15203671830177853</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.13777777777777778</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" ref="I24:J24" si="53">I7/I3</f>
+        <v>0.12871287128712872</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.13</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" ref="L24:M24" si="54">L7/L3</f>
+        <v>0.15047291487532244</v>
+      </c>
+      <c r="M24" s="9">
         <f t="shared" si="54"/>
-        <v>0.15034562211981567</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" si="54"/>
-        <v>0.13563692625064466</v>
-      </c>
-      <c r="F24" s="9">
-        <f t="shared" si="54"/>
-        <v>0.13428571428571429</v>
-      </c>
-      <c r="G24" s="9">
-        <f t="shared" si="54"/>
-        <v>0.15203671830177853</v>
-      </c>
-      <c r="H24" s="9">
-        <f t="shared" si="54"/>
-        <v>0.13777777777777778</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" ref="I24:J24" si="55">I7/I3</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J24" s="9">
-        <f t="shared" si="55"/>
-        <v>0.13</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" ref="L24:M24" si="56">L7/L3</f>
-        <v>0.15047291487532244</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="56"/>
         <v>0.1183328475663072</v>
       </c>
       <c r="N24" s="9">
@@ -3367,46 +3374,46 @@
       </c>
       <c r="R24" s="9">
         <f>R7/R3</f>
-        <v>0.1394407720782655</v>
+        <v>0.13662246386420898</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:AB24" si="57">S7/S3</f>
+        <f t="shared" ref="S24:AB24" si="55">S7/S3</f>
         <v>0.13</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13</v>
       </c>
       <c r="AD24" t="s">
@@ -3414,7 +3421,7 @@
       </c>
       <c r="AE24" s="5">
         <f>NPV(AE23,R17:EK17)</f>
-        <v>613.67572789379051</v>
+        <v>607.38884694086323</v>
       </c>
     </row>
     <row r="25" spans="2:141" x14ac:dyDescent="0.3">
@@ -3434,16 +3441,16 @@
         <v>0.12574850299401197</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" ref="I25:J25" si="58">I8/E8-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="I25:J25" si="56">I8/E8-1</f>
+        <v>2.8409090909090828E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9">
-        <f t="shared" ref="M25" si="59">M8/L8-1</f>
+        <f t="shared" ref="M25" si="57">M8/L8-1</f>
         <v>0.51020408163265318</v>
       </c>
       <c r="N25" s="9">
@@ -3464,46 +3471,46 @@
       </c>
       <c r="R25" s="9">
         <f>R8/Q8-1</f>
-        <v>8.5634588563458847E-2</v>
+        <v>6.8061366806136725E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:AB25" si="60">S8/R8-1</f>
+        <f t="shared" ref="S25:AB25" si="58">S8/R8-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD25" t="s">
@@ -3511,7 +3518,7 @@
       </c>
       <c r="AE25" s="5">
         <f>Main!D8</f>
-        <v>-186.5</v>
+        <v>-174.5</v>
       </c>
     </row>
     <row r="26" spans="2:141" x14ac:dyDescent="0.3">
@@ -3519,43 +3526,43 @@
         <v>40</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:H26" si="61">C10/C3</f>
+        <f t="shared" ref="C26:H26" si="59">C10/C3</f>
         <v>-6.0233918128654952E-2</v>
       </c>
       <c r="D26" s="9">
+        <f t="shared" si="59"/>
+        <v>-3.5138248847926316E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="59"/>
+        <v>-4.6415678184630813E-3</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="59"/>
+        <v>-1.2857142857142871E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="59"/>
+        <v>-2.6391279403327562E-2</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="59"/>
+        <v>-1.9999999999999969E-2</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" ref="I26:J26" si="60">I10/I3</f>
+        <v>-1.0422094841063054E-2</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="60"/>
+        <v>-5.9644059644057342E-4</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" ref="L26:M26" si="61">L10/L3</f>
+        <v>-7.6096302665520227E-2</v>
+      </c>
+      <c r="M26" s="9">
         <f t="shared" si="61"/>
-        <v>-3.5138248847926316E-2</v>
-      </c>
-      <c r="E26" s="9">
-        <f t="shared" si="61"/>
-        <v>-4.6415678184630813E-3</v>
-      </c>
-      <c r="F26" s="9">
-        <f t="shared" si="61"/>
-        <v>-1.2857142857142871E-2</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="61"/>
-        <v>-2.6391279403327562E-2</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="61"/>
-        <v>-1.9999999999999969E-2</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" ref="I26:J26" si="62">I10/I3</f>
-        <v>-6.7368421052632389E-3</v>
-      </c>
-      <c r="J26" s="9">
-        <f t="shared" si="62"/>
-        <v>4.5638849599245138E-3</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" ref="L26:M26" si="63">L10/L3</f>
-        <v>-7.6096302665520227E-2</v>
-      </c>
-      <c r="M26" s="9">
-        <f t="shared" si="63"/>
         <v>-3.9930049548236632E-2</v>
       </c>
       <c r="N26" s="9">
@@ -3576,54 +3583,54 @@
       </c>
       <c r="R26" s="9">
         <f>R10/R3</f>
-        <v>-1.1253305129561155E-2</v>
+        <v>-1.369049197719137E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:AB26" si="64">S10/S3</f>
-        <v>8.3654767344549769E-2</v>
+        <f t="shared" ref="S26:AB26" si="62">S10/S3</f>
+        <v>8.3013721069915808E-2</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.060006102629474E-2</v>
+        <f t="shared" si="62"/>
+        <v>8.9956300405916206E-2</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.0841030179567642E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.020037416162266E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.0612738048655606E-2</v>
+        <f t="shared" si="62"/>
+        <v>8.9969140756711183E-2</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.143534811943349E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.0785155707357082E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.3480099608458697E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.283628163179472E-2</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.5504804514258121E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.4867298478541806E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.7509659371961419E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.6878403395418797E-2</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="64"/>
-        <v>9.9494858789883373E-2</v>
+        <f t="shared" si="62"/>
+        <v>9.8869791597424525E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="64"/>
-        <v>0.10146059546841402</v>
+        <f t="shared" si="62"/>
+        <v>0.10084165638568515</v>
       </c>
       <c r="AD26" t="s">
         <v>46</v>
       </c>
       <c r="AE26" s="5">
         <f>AE24+AE25</f>
-        <v>427.17572789379051</v>
+        <v>432.88884694086323</v>
       </c>
     </row>
     <row r="27" spans="2:141" x14ac:dyDescent="0.3">
@@ -3631,43 +3638,43 @@
         <v>26</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:H27" si="65">C16/C15</f>
+        <f t="shared" ref="C27:H27" si="63">C16/C15</f>
         <v>2.150537634408603E-2</v>
       </c>
       <c r="D27" s="9">
+        <f t="shared" si="63"/>
+        <v>-8.1081081081081252E-2</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="63"/>
+        <v>2.3333333333333992</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="63"/>
+        <v>0.39999999999999963</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="63"/>
+        <v>-2.7027027027027074E-2</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="63"/>
+        <v>-2.1739130434782636E-2</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" ref="I27:J27" si="64">I16/I15</f>
+        <v>0.65714285714285714</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" ref="L27:M27" si="65">L16/L15</f>
+        <v>1.1568627450980389</v>
+      </c>
+      <c r="M27" s="9">
         <f t="shared" si="65"/>
-        <v>-8.1081081081081252E-2</v>
-      </c>
-      <c r="E27" s="9">
-        <f t="shared" si="65"/>
-        <v>2.3333333333333992</v>
-      </c>
-      <c r="F27" s="9">
-        <f t="shared" si="65"/>
-        <v>0.39999999999999963</v>
-      </c>
-      <c r="G27" s="9">
-        <f t="shared" si="65"/>
-        <v>-2.7027027027027074E-2</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="65"/>
-        <v>-2.1739130434782636E-2</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" ref="I27:J27" si="66">I16/I15</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" ref="L27:M27" si="67">L16/L15</f>
-        <v>1.1568627450980389</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="67"/>
         <v>-0.51369863013698647</v>
       </c>
       <c r="N27" s="9">
@@ -3688,46 +3695,46 @@
       </c>
       <c r="R27" s="9">
         <f>R16/R15</f>
-        <v>-1.5857913098636149E-2</v>
+        <v>0.15081873024992803</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" ref="S27:AB27" si="68">S16/S15</f>
+        <f t="shared" ref="S27:AB27" si="66">S16/S15</f>
         <v>0</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AD27" t="s">
@@ -3735,7 +3742,7 @@
       </c>
       <c r="AE27" s="4">
         <f>AE26/AB18</f>
-        <v>15.201983199067277</v>
+        <v>14.146694344472653</v>
       </c>
     </row>
     <row r="28" spans="2:141" x14ac:dyDescent="0.3">
@@ -3743,43 +3750,43 @@
         <v>41</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:H28" si="69">C17/C3</f>
+        <f t="shared" ref="C28:H28" si="67">C17/C3</f>
         <v>-5.3216374269005835E-2</v>
       </c>
       <c r="D28" s="9">
+        <f t="shared" si="67"/>
+        <v>2.3041474654377836E-2</v>
+      </c>
+      <c r="E28" s="9">
+        <f t="shared" si="67"/>
+        <v>2.0629190304280991E-3</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="67"/>
+        <v>-8.571428571428584E-3</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" si="67"/>
+        <v>-2.1801491681009717E-2</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="67"/>
+        <v>-2.6111111111111078E-2</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" ref="I28:J28" si="68">I17/I3</f>
+        <v>-6.253256904637833E-3</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="68"/>
+        <v>-1.0216450216450193E-2</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" ref="L28:M28" si="69">L17/L3</f>
+        <v>1.0318142734307811E-2</v>
+      </c>
+      <c r="M28" s="9">
         <f t="shared" si="69"/>
-        <v>2.3041474654377836E-2</v>
-      </c>
-      <c r="E28" s="9">
-        <f t="shared" si="69"/>
-        <v>2.0629190304280991E-3</v>
-      </c>
-      <c r="F28" s="9">
-        <f t="shared" si="69"/>
-        <v>-8.571428571428584E-3</v>
-      </c>
-      <c r="G28" s="9">
-        <f t="shared" si="69"/>
-        <v>-2.1801491681009717E-2</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="69"/>
-        <v>-2.6111111111111078E-2</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" ref="I28:J28" si="70">I17/I3</f>
-        <v>-1.7263157894736921E-2</v>
-      </c>
-      <c r="J28" s="9">
-        <f t="shared" si="70"/>
-        <v>-4.8656294200849163E-3</v>
-      </c>
-      <c r="L28" s="9">
-        <f t="shared" ref="L28:M28" si="71">L17/L3</f>
-        <v>1.0318142734307811E-2</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" si="71"/>
         <v>-0.1288254153308073</v>
       </c>
       <c r="N28" s="9">
@@ -3800,54 +3807,54 @@
       </c>
       <c r="R28" s="9">
         <f>R17/R3</f>
-        <v>-1.693812797461668E-2</v>
+        <v>-1.5679618087786781E-2</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28:AB28" si="72">S17/S3</f>
-        <v>7.9611599143618428E-2</v>
+        <f t="shared" ref="S28:AB28" si="70">S17/S3</f>
+        <v>7.9601004703698186E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="72"/>
-        <v>8.6437976113571291E-2</v>
+        <f t="shared" si="70"/>
+        <v>8.6443210028927478E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="72"/>
-        <v>8.655653100470527E-2</v>
+        <f t="shared" si="70"/>
+        <v>8.6583957597075434E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="72"/>
-        <v>8.6202224192179641E-2</v>
+        <f t="shared" si="70"/>
+        <v>8.6246358999089043E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="72"/>
-        <v>8.6895113267178831E-2</v>
+        <f t="shared" si="70"/>
+        <v>8.6952880368628402E-2</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="72"/>
-        <v>8.8806328437020063E-2</v>
+        <f t="shared" si="70"/>
+        <v>8.8891292312515219E-2</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="72"/>
-        <v>9.0693569484835992E-2</v>
+        <f t="shared" si="70"/>
+        <v>9.0806280061636435E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="72"/>
-        <v>9.2556917429909236E-2</v>
+        <f t="shared" si="70"/>
+        <v>9.2697943260369134E-2</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="72"/>
-        <v>9.4396447967182606E-2</v>
+        <f t="shared" si="70"/>
+        <v>9.456637675252047E-2</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="72"/>
-        <v>9.6212231386222036E-2</v>
+        <f t="shared" si="70"/>
+        <v>9.6411670515930983E-2</v>
       </c>
       <c r="AD28" t="s">
         <v>48</v>
       </c>
       <c r="AE28" s="4">
         <f>Main!D3</f>
-        <v>17.52</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="29" spans="2:141" x14ac:dyDescent="0.3">
@@ -3856,7 +3863,7 @@
       </c>
       <c r="AE29" s="10">
         <f>AE27/AE28-1</f>
-        <v>-0.1323068950304066</v>
+        <v>-0.1218687557745094</v>
       </c>
     </row>
     <row r="30" spans="2:141" x14ac:dyDescent="0.3">
@@ -3872,96 +3879,96 @@
         <v>52</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:G32" si="73">C17</f>
+        <f t="shared" ref="C32:G32" si="71">C17</f>
         <v>-9.0999999999999979</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.999999999999992</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.40000000000000846</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-1.8000000000000027</v>
       </c>
       <c r="G32" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-3.799999999999994</v>
       </c>
       <c r="H32" s="8">
         <f>H17</f>
         <v>-4.699999999999994</v>
       </c>
-      <c r="I32" s="8">
-        <f t="shared" ref="I32:J32" si="74">I17</f>
-        <v>-3.2800000000000153</v>
+      <c r="I32" s="11">
+        <f t="shared" ref="I32:J32" si="72">I17</f>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="J32" s="8">
+        <f t="shared" si="72"/>
+        <v>-2.1239999999999952</v>
+      </c>
+      <c r="N32" s="8">
+        <f t="shared" ref="N32:O32" si="73">N17</f>
+        <v>-27.500000000000011</v>
+      </c>
+      <c r="O32" s="8">
+        <f t="shared" si="73"/>
+        <v>19.700000000000049</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" ref="P32:R32" si="74">P17</f>
+        <v>-16.400000000000023</v>
+      </c>
+      <c r="Q32" s="8">
         <f t="shared" si="74"/>
-        <v>-1.0320000000000107</v>
-      </c>
-      <c r="N32" s="8">
-        <f t="shared" ref="N32:O32" si="75">N17</f>
-        <v>-27.500000000000011</v>
-      </c>
-      <c r="O32" s="8">
+        <v>-6.4999999999999982</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="74"/>
+        <v>-11.824000000000012</v>
+      </c>
+      <c r="S32" s="8">
+        <f t="shared" ref="S32:AB32" si="75">S17</f>
+        <v>61.227659999999979</v>
+      </c>
+      <c r="T32" s="8">
         <f t="shared" si="75"/>
-        <v>19.700000000000049</v>
-      </c>
-      <c r="P32" s="8">
-        <f t="shared" ref="P32:R32" si="76">P17</f>
-        <v>-16.400000000000023</v>
-      </c>
-      <c r="Q32" s="8">
-        <f t="shared" si="76"/>
-        <v>-6.4999999999999982</v>
-      </c>
-      <c r="R32" s="8">
-        <f t="shared" si="76"/>
-        <v>-12.812000000000056</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" ref="S32:AB32" si="77">S17</f>
-        <v>62.024759999999965</v>
-      </c>
-      <c r="T32" s="8">
-        <f t="shared" si="77"/>
-        <v>68.689998399999979</v>
+        <v>67.820372399999911</v>
       </c>
       <c r="U32" s="8">
-        <f t="shared" si="77"/>
-        <v>70.159895087999971</v>
+        <f t="shared" si="75"/>
+        <v>69.289414067999999</v>
       </c>
       <c r="V32" s="8">
-        <f t="shared" si="77"/>
-        <v>71.270159676960049</v>
+        <f t="shared" si="75"/>
+        <v>70.399633411559975</v>
       </c>
       <c r="W32" s="8">
-        <f t="shared" si="77"/>
-        <v>73.27988609169121</v>
+        <f t="shared" si="75"/>
+        <v>72.395866823053154</v>
       </c>
       <c r="X32" s="8">
-        <f t="shared" si="77"/>
-        <v>76.389473874304315</v>
+        <f t="shared" si="75"/>
+        <v>75.489959336113031</v>
       </c>
       <c r="Y32" s="8">
-        <f t="shared" si="77"/>
-        <v>79.573098699552432</v>
+        <f t="shared" si="75"/>
+        <v>78.658566606512579</v>
       </c>
       <c r="Z32" s="8">
-        <f t="shared" si="77"/>
-        <v>82.832130030476847</v>
+        <f t="shared" si="75"/>
+        <v>81.903113816234992</v>
       </c>
       <c r="AA32" s="8">
-        <f t="shared" si="77"/>
-        <v>86.167952120067582</v>
+        <f t="shared" si="75"/>
+        <v>85.225044427659896</v>
       </c>
       <c r="AB32" s="8">
-        <f t="shared" si="77"/>
-        <v>89.581963606742363</v>
+        <f t="shared" si="75"/>
+        <v>88.625819968332976</v>
       </c>
     </row>
     <row r="33" spans="2:149" x14ac:dyDescent="0.3">
@@ -3986,7 +3993,7 @@
       <c r="H33" s="5">
         <v>0.1</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="12">
         <v>0</v>
       </c>
       <c r="J33" s="5">
@@ -4062,7 +4069,7 @@
       <c r="H34" s="5">
         <v>0.5</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="12">
         <v>0.8</v>
       </c>
       <c r="J34" s="5">
@@ -4078,51 +4085,51 @@
         <v>0.8</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" ref="Q34:Q40" si="78">SUM(C34:F34)</f>
+        <f t="shared" ref="Q34:Q40" si="76">SUM(C34:F34)</f>
         <v>1.9000000000000001</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" ref="R34:R40" si="79">SUM(G34:J34)</f>
+        <f t="shared" ref="R34:R40" si="77">SUM(G34:J34)</f>
         <v>2.8</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" ref="S34:AB34" si="80">R34*1.05</f>
+        <f t="shared" ref="S34:AB34" si="78">R34*1.05</f>
         <v>2.94</v>
       </c>
       <c r="T34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.0870000000000002</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.2413500000000002</v>
       </c>
       <c r="V34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.4034175000000002</v>
       </c>
       <c r="W34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.5735883750000004</v>
       </c>
       <c r="X34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.7522677937500006</v>
       </c>
       <c r="Y34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.9398811834375009</v>
       </c>
       <c r="Z34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>4.136875242609376</v>
       </c>
       <c r="AA34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>4.3437190047398451</v>
       </c>
       <c r="AB34" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>4.5609049549768379</v>
       </c>
     </row>
@@ -4148,7 +4155,7 @@
       <c r="H35" s="5">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="12">
         <v>9</v>
       </c>
       <c r="J35" s="5">
@@ -4164,11 +4171,11 @@
         <v>24.4</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>31.8</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>35</v>
       </c>
       <c r="S35" s="5">
@@ -4188,7 +4195,7 @@
         <v>40.153931999999998</v>
       </c>
       <c r="W35" s="5">
-        <f t="shared" ref="W35" si="81">V35*1.02</f>
+        <f t="shared" ref="W35" si="79">V35*1.02</f>
         <v>40.95701064</v>
       </c>
       <c r="X35" s="5">
@@ -4196,19 +4203,19 @@
         <v>41.366580746400004</v>
       </c>
       <c r="Y35" s="5">
-        <f t="shared" ref="Y35:AB35" si="82">X35*1.01</f>
+        <f t="shared" ref="Y35:AB35" si="80">X35*1.01</f>
         <v>41.780246553864004</v>
       </c>
       <c r="Z35" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>42.198049019402646</v>
       </c>
       <c r="AA35" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>42.620029509596669</v>
       </c>
       <c r="AB35" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>43.046229804692636</v>
       </c>
     </row>
@@ -4234,7 +4241,7 @@
       <c r="H36" s="5">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="12">
         <f>E36*1.05</f>
         <v>4.620000000000001</v>
       </c>
@@ -4252,11 +4259,11 @@
         <v>17.3</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>17.5</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>18.14</v>
       </c>
       <c r="S36" s="5">
@@ -4264,39 +4271,39 @@
         <v>18.502800000000001</v>
       </c>
       <c r="T36" s="5">
-        <f t="shared" ref="T36:AB36" si="83">S36*1.01</f>
+        <f t="shared" ref="T36:AB36" si="81">S36*1.01</f>
         <v>18.687828</v>
       </c>
       <c r="U36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>18.874706279999998</v>
       </c>
       <c r="V36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>19.063453342799999</v>
       </c>
       <c r="W36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>19.254087876227999</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>19.446628754990279</v>
       </c>
       <c r="Y36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>19.641095042540183</v>
       </c>
       <c r="Z36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>19.837505992965585</v>
       </c>
       <c r="AA36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>20.035881052895242</v>
       </c>
       <c r="AB36" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>20.236239863424196</v>
       </c>
     </row>
@@ -4322,7 +4329,7 @@
       <c r="H37" s="5">
         <v>12.5</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="12">
         <f>E37*1.1</f>
         <v>12.540000000000001</v>
       </c>
@@ -4340,11 +4347,11 @@
         <v>37</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>48.3</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>53.16</v>
       </c>
       <c r="S37" s="5"/>
@@ -4380,7 +4387,7 @@
       <c r="H38" s="5">
         <v>0</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="12">
         <v>0</v>
       </c>
       <c r="J38" s="5">
@@ -4396,11 +4403,11 @@
         <v>4</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>2.5</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="S38" s="5">
@@ -4456,7 +4463,7 @@
       <c r="H39" s="5">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="12">
         <v>0</v>
       </c>
       <c r="J39" s="5">
@@ -4472,51 +4479,51 @@
         <v>-12.8</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-10.3</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>-1.1000000000000001</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:AB39" si="84">R39*1.05</f>
+        <f t="shared" ref="S39:AB39" si="82">R39*1.05</f>
         <v>-1.1550000000000002</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.2127500000000002</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.2733875000000003</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.3370568750000005</v>
       </c>
       <c r="W39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.4039097187500005</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.4741052046875005</v>
       </c>
       <c r="Y39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.5478104649218756</v>
       </c>
       <c r="Z39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.6252009881679694</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.706461037576368</v>
       </c>
       <c r="AB39" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-1.7917840894551864</v>
       </c>
     </row>
@@ -4542,7 +4549,7 @@
       <c r="H40" s="5">
         <v>0.3</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="12">
         <v>0</v>
       </c>
       <c r="J40" s="5">
@@ -4559,11 +4566,11 @@
         <v>-3.2</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-0.5</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>0.8</v>
       </c>
       <c r="S40" s="5">
@@ -4610,572 +4617,572 @@
         <v>18.79999999999999</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" ref="E41:H41" si="85">E32+SUM(E33:E40)</f>
+        <f>E32+SUM(E33:E40)</f>
         <v>23.900000000000009</v>
       </c>
       <c r="F41" s="8">
-        <f t="shared" si="85"/>
+        <f>F32+SUM(F33:F40)</f>
         <v>23.399999999999995</v>
       </c>
       <c r="G41" s="8">
-        <f t="shared" si="85"/>
+        <f>G32+SUM(G33:G40)</f>
         <v>22.100000000000005</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="85"/>
+        <f>H32+SUM(H33:H40)</f>
         <v>22.100000000000009</v>
       </c>
-      <c r="I41" s="8">
-        <f t="shared" ref="I41" si="86">I32+SUM(I33:I40)</f>
-        <v>23.679999999999986</v>
+      <c r="I41" s="11">
+        <f>I32+SUM(I33:I40)</f>
+        <v>25.76</v>
       </c>
       <c r="J41" s="8">
-        <f t="shared" ref="J41" si="87">J32+SUM(J33:J40)</f>
-        <v>28.10799999999999</v>
+        <f>J32+SUM(J33:J40)</f>
+        <v>27.016000000000005</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" ref="N41:R41" si="88">N32+SUM(N33:N40)</f>
+        <f>N32+SUM(N33:N40)</f>
         <v>49.399999999999977</v>
       </c>
       <c r="O41" s="8">
-        <f t="shared" si="88"/>
+        <f>O32+SUM(O33:O40)</f>
         <v>34.700000000000045</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="88"/>
+        <f>P32+SUM(P33:P40)</f>
         <v>48.09999999999998</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="88"/>
+        <f>Q32+SUM(Q33:Q40)</f>
         <v>82.3</v>
       </c>
       <c r="R41" s="8">
-        <f t="shared" si="88"/>
-        <v>95.987999999999943</v>
+        <f>R32+SUM(R33:R40)</f>
+        <v>96.975999999999985</v>
       </c>
       <c r="S41" s="8">
-        <f t="shared" ref="S41" si="89">S32+SUM(S33:S40)</f>
-        <v>119.06255999999996</v>
+        <f>S32+SUM(S33:S40)</f>
+        <v>118.26545999999998</v>
       </c>
       <c r="T41" s="8">
-        <f t="shared" ref="T41" si="90">T32+SUM(T33:T40)</f>
-        <v>127.47207639999998</v>
+        <f>T32+SUM(T33:T40)</f>
+        <v>126.60245039999991</v>
       </c>
       <c r="U41" s="8">
-        <f t="shared" ref="U41" si="91">U32+SUM(U33:U40)</f>
-        <v>130.36916386799996</v>
+        <f>U32+SUM(U33:U40)</f>
+        <v>129.49868284799999</v>
       </c>
       <c r="V41" s="8">
-        <f t="shared" ref="V41" si="92">V32+SUM(V33:V40)</f>
-        <v>132.55390564476005</v>
+        <f>V32+SUM(V33:V40)</f>
+        <v>131.68337937935996</v>
       </c>
       <c r="W41" s="8">
-        <f t="shared" ref="W41" si="93">W32+SUM(W33:W40)</f>
-        <v>135.66066326416922</v>
+        <f>W32+SUM(W33:W40)</f>
+        <v>134.77664399553115</v>
       </c>
       <c r="X41" s="8">
-        <f t="shared" ref="X41" si="94">X32+SUM(X33:X40)</f>
-        <v>139.48084596475709</v>
+        <f>X32+SUM(X33:X40)</f>
+        <v>138.58133142656581</v>
       </c>
       <c r="Y41" s="8">
-        <f t="shared" ref="Y41" si="95">Y32+SUM(Y33:Y40)</f>
-        <v>143.38651101447223</v>
+        <f>Y32+SUM(Y33:Y40)</f>
+        <v>142.4719789214324</v>
       </c>
       <c r="Z41" s="8">
-        <f t="shared" ref="Z41" si="96">Z32+SUM(Z33:Z40)</f>
-        <v>147.3793592972865</v>
+        <f>Z32+SUM(Z33:Z40)</f>
+        <v>146.45034308304463</v>
       </c>
       <c r="AA41" s="8">
-        <f t="shared" ref="AA41" si="97">AA32+SUM(AA33:AA40)</f>
-        <v>151.46112064972294</v>
+        <f>AA32+SUM(AA33:AA40)</f>
+        <v>150.51821295731526</v>
       </c>
       <c r="AB41" s="8">
-        <f t="shared" ref="AB41" si="98">AB32+SUM(AB33:AB40)</f>
-        <v>155.63355414038085</v>
+        <f>AB32+SUM(AB33:AB40)</f>
+        <v>154.67741050197145</v>
       </c>
       <c r="AC41" s="1">
         <f>AB41*(1+$AE$22)</f>
-        <v>154.07721859897705</v>
+        <v>153.13063639695173</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" ref="AD41:CO41" si="99">AC41*(1+$AE$22)</f>
-        <v>152.53644641298729</v>
+        <f t="shared" ref="AD41:CO41" si="83">AC41*(1+$AE$22)</f>
+        <v>151.59933003298221</v>
       </c>
       <c r="AE41" s="1">
-        <f t="shared" si="99"/>
-        <v>151.01108194885742</v>
+        <f t="shared" si="83"/>
+        <v>150.08333673265238</v>
       </c>
       <c r="AF41" s="1">
-        <f t="shared" si="99"/>
-        <v>149.50097112936885</v>
+        <f t="shared" si="83"/>
+        <v>148.58250336532586</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="99"/>
-        <v>148.00596141807517</v>
+        <f t="shared" si="83"/>
+        <v>147.09667833167259</v>
       </c>
       <c r="AH41" s="1">
-        <f t="shared" si="99"/>
-        <v>146.52590180389441</v>
+        <f t="shared" si="83"/>
+        <v>145.62571154835587</v>
       </c>
       <c r="AI41" s="1">
-        <f t="shared" si="99"/>
-        <v>145.06064278585546</v>
+        <f t="shared" si="83"/>
+        <v>144.1694544328723</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="99"/>
-        <v>143.6100363579969</v>
+        <f t="shared" si="83"/>
+        <v>142.72775988854357</v>
       </c>
       <c r="AK41" s="1">
-        <f t="shared" si="99"/>
-        <v>142.17393599441692</v>
+        <f t="shared" si="83"/>
+        <v>141.30048228965813</v>
       </c>
       <c r="AL41" s="1">
-        <f t="shared" si="99"/>
-        <v>140.75219663447274</v>
+        <f t="shared" si="83"/>
+        <v>139.88747746676154</v>
       </c>
       <c r="AM41" s="1">
-        <f t="shared" si="99"/>
-        <v>139.34467466812802</v>
+        <f t="shared" si="83"/>
+        <v>138.48860269209393</v>
       </c>
       <c r="AN41" s="1">
-        <f t="shared" si="99"/>
-        <v>137.95122792144673</v>
+        <f t="shared" si="83"/>
+        <v>137.10371666517298</v>
       </c>
       <c r="AO41" s="1">
-        <f t="shared" si="99"/>
-        <v>136.57171564223225</v>
+        <f t="shared" si="83"/>
+        <v>135.73267949852126</v>
       </c>
       <c r="AP41" s="1">
-        <f t="shared" si="99"/>
-        <v>135.20599848580991</v>
+        <f t="shared" si="83"/>
+        <v>134.37535270353604</v>
       </c>
       <c r="AQ41" s="1">
-        <f t="shared" si="99"/>
-        <v>133.85393850095181</v>
+        <f t="shared" si="83"/>
+        <v>133.03159917650066</v>
       </c>
       <c r="AR41" s="1">
-        <f t="shared" si="99"/>
-        <v>132.5153991159423</v>
+        <f t="shared" si="83"/>
+        <v>131.70128318473564</v>
       </c>
       <c r="AS41" s="1">
-        <f t="shared" si="99"/>
-        <v>131.19024512478288</v>
+        <f t="shared" si="83"/>
+        <v>130.38427035288828</v>
       </c>
       <c r="AT41" s="1">
-        <f t="shared" si="99"/>
-        <v>129.87834267353506</v>
+        <f t="shared" si="83"/>
+        <v>129.08042764935939</v>
       </c>
       <c r="AU41" s="1">
-        <f t="shared" si="99"/>
-        <v>128.5795592467997</v>
+        <f t="shared" si="83"/>
+        <v>127.7896233728658</v>
       </c>
       <c r="AV41" s="1">
-        <f t="shared" si="99"/>
-        <v>127.29376365433171</v>
+        <f t="shared" si="83"/>
+        <v>126.51172713913715</v>
       </c>
       <c r="AW41" s="1">
-        <f t="shared" si="99"/>
-        <v>126.02082601778839</v>
+        <f t="shared" si="83"/>
+        <v>125.24660986774578</v>
       </c>
       <c r="AX41" s="1">
-        <f t="shared" si="99"/>
-        <v>124.7606177576105</v>
+        <f t="shared" si="83"/>
+        <v>123.99414376906832</v>
       </c>
       <c r="AY41" s="1">
-        <f t="shared" si="99"/>
-        <v>123.5130115800344</v>
+        <f t="shared" si="83"/>
+        <v>122.75420233137763</v>
       </c>
       <c r="AZ41" s="1">
-        <f t="shared" si="99"/>
-        <v>122.27788146423406</v>
+        <f t="shared" si="83"/>
+        <v>121.52666030806385</v>
       </c>
       <c r="BA41" s="1">
-        <f t="shared" si="99"/>
-        <v>121.05510264959172</v>
+        <f t="shared" si="83"/>
+        <v>120.31139370498322</v>
       </c>
       <c r="BB41" s="1">
-        <f t="shared" si="99"/>
-        <v>119.8445516230958</v>
+        <f t="shared" si="83"/>
+        <v>119.10827976793338</v>
       </c>
       <c r="BC41" s="1">
-        <f t="shared" si="99"/>
-        <v>118.64610610686483</v>
+        <f t="shared" si="83"/>
+        <v>117.91719697025405</v>
       </c>
       <c r="BD41" s="1">
-        <f t="shared" si="99"/>
-        <v>117.45964504579618</v>
+        <f t="shared" si="83"/>
+        <v>116.73802500055152</v>
       </c>
       <c r="BE41" s="1">
-        <f t="shared" si="99"/>
-        <v>116.28504859533821</v>
+        <f t="shared" si="83"/>
+        <v>115.57064475054599</v>
       </c>
       <c r="BF41" s="1">
-        <f t="shared" si="99"/>
-        <v>115.12219810938483</v>
+        <f t="shared" si="83"/>
+        <v>114.41493830304053</v>
       </c>
       <c r="BG41" s="1">
-        <f t="shared" si="99"/>
-        <v>113.97097612829097</v>
+        <f t="shared" si="83"/>
+        <v>113.27078892001012</v>
       </c>
       <c r="BH41" s="1">
-        <f t="shared" si="99"/>
-        <v>112.83126636700806</v>
+        <f t="shared" si="83"/>
+        <v>112.13808103081001</v>
       </c>
       <c r="BI41" s="1">
-        <f t="shared" si="99"/>
-        <v>111.70295370333797</v>
+        <f t="shared" si="83"/>
+        <v>111.01670022050192</v>
       </c>
       <c r="BJ41" s="1">
-        <f t="shared" si="99"/>
-        <v>110.58592416630459</v>
+        <f t="shared" si="83"/>
+        <v>109.9065332182969</v>
       </c>
       <c r="BK41" s="1">
-        <f t="shared" si="99"/>
-        <v>109.48006492464155</v>
+        <f t="shared" si="83"/>
+        <v>108.80746788611393</v>
       </c>
       <c r="BL41" s="1">
-        <f t="shared" si="99"/>
-        <v>108.38526427539513</v>
+        <f t="shared" si="83"/>
+        <v>107.71939320725279</v>
       </c>
       <c r="BM41" s="1">
-        <f t="shared" si="99"/>
-        <v>107.30141163264118</v>
+        <f t="shared" si="83"/>
+        <v>106.64219927518026</v>
       </c>
       <c r="BN41" s="1">
-        <f t="shared" si="99"/>
-        <v>106.22839751631476</v>
+        <f t="shared" si="83"/>
+        <v>105.57577728242846</v>
       </c>
       <c r="BO41" s="1">
-        <f t="shared" si="99"/>
-        <v>105.1661135411516</v>
+        <f t="shared" si="83"/>
+        <v>104.52001950960418</v>
       </c>
       <c r="BP41" s="1">
-        <f t="shared" si="99"/>
-        <v>104.11445240574008</v>
+        <f t="shared" si="83"/>
+        <v>103.47481931450814</v>
       </c>
       <c r="BQ41" s="1">
-        <f t="shared" si="99"/>
-        <v>103.07330788168268</v>
+        <f t="shared" si="83"/>
+        <v>102.44007112136306</v>
       </c>
       <c r="BR41" s="1">
-        <f t="shared" si="99"/>
-        <v>102.04257480286586</v>
+        <f t="shared" si="83"/>
+        <v>101.41567041014943</v>
       </c>
       <c r="BS41" s="1">
-        <f t="shared" si="99"/>
-        <v>101.0221490548372</v>
+        <f t="shared" si="83"/>
+        <v>100.40151370604794</v>
       </c>
       <c r="BT41" s="1">
-        <f t="shared" si="99"/>
-        <v>100.01192756428883</v>
+        <f t="shared" si="83"/>
+        <v>99.397498568987459</v>
       </c>
       <c r="BU41" s="1">
-        <f t="shared" si="99"/>
-        <v>99.011808288645938</v>
+        <f t="shared" si="83"/>
+        <v>98.403523583297584</v>
       </c>
       <c r="BV41" s="1">
-        <f t="shared" si="99"/>
-        <v>98.021690205759484</v>
+        <f t="shared" si="83"/>
+        <v>97.419488347464608</v>
       </c>
       <c r="BW41" s="1">
-        <f t="shared" si="99"/>
-        <v>97.041473303701892</v>
+        <f t="shared" si="83"/>
+        <v>96.445293463989955</v>
       </c>
       <c r="BX41" s="1">
-        <f t="shared" si="99"/>
-        <v>96.071058570664874</v>
+        <f t="shared" si="83"/>
+        <v>95.480840529350061</v>
       </c>
       <c r="BY41" s="1">
-        <f t="shared" si="99"/>
-        <v>95.110347984958224</v>
+        <f t="shared" si="83"/>
+        <v>94.526032124056556</v>
       </c>
       <c r="BZ41" s="1">
-        <f t="shared" si="99"/>
-        <v>94.159244505108646</v>
+        <f t="shared" si="83"/>
+        <v>93.580771802815988</v>
       </c>
       <c r="CA41" s="1">
-        <f t="shared" si="99"/>
-        <v>93.21765206005756</v>
+        <f t="shared" si="83"/>
+        <v>92.64496408478783</v>
       </c>
       <c r="CB41" s="1">
-        <f t="shared" si="99"/>
-        <v>92.285475539456982</v>
+        <f t="shared" si="83"/>
+        <v>91.718514443939952</v>
       </c>
       <c r="CC41" s="1">
-        <f t="shared" si="99"/>
-        <v>91.362620784062415</v>
+        <f t="shared" si="83"/>
+        <v>90.801329299500551</v>
       </c>
       <c r="CD41" s="1">
-        <f t="shared" si="99"/>
-        <v>90.448994576221793</v>
+        <f t="shared" si="83"/>
+        <v>89.893316006505543</v>
       </c>
       <c r="CE41" s="1">
-        <f t="shared" si="99"/>
-        <v>89.544504630459571</v>
+        <f t="shared" si="83"/>
+        <v>88.994382846440487</v>
       </c>
       <c r="CF41" s="1">
-        <f t="shared" si="99"/>
-        <v>88.649059584154969</v>
+        <f t="shared" si="83"/>
+        <v>88.104439017976077</v>
       </c>
       <c r="CG41" s="1">
-        <f t="shared" si="99"/>
-        <v>87.762568988313419</v>
+        <f t="shared" si="83"/>
+        <v>87.22339462779631</v>
       </c>
       <c r="CH41" s="1">
-        <f t="shared" si="99"/>
-        <v>86.884943298430287</v>
+        <f t="shared" si="83"/>
+        <v>86.351160681518351</v>
       </c>
       <c r="CI41" s="1">
-        <f t="shared" si="99"/>
-        <v>86.016093865445981</v>
+        <f t="shared" si="83"/>
+        <v>85.487649074703171</v>
       </c>
       <c r="CJ41" s="1">
-        <f t="shared" si="99"/>
-        <v>85.155932926791522</v>
+        <f t="shared" si="83"/>
+        <v>84.63277258395614</v>
       </c>
       <c r="CK41" s="1">
-        <f t="shared" si="99"/>
-        <v>84.304373597523607</v>
+        <f t="shared" si="83"/>
+        <v>83.786444858116582</v>
       </c>
       <c r="CL41" s="1">
-        <f t="shared" si="99"/>
-        <v>83.461329861548364</v>
+        <f t="shared" si="83"/>
+        <v>82.94858040953541</v>
       </c>
       <c r="CM41" s="1">
-        <f t="shared" si="99"/>
-        <v>82.626716562932884</v>
+        <f t="shared" si="83"/>
+        <v>82.119094605440054</v>
       </c>
       <c r="CN41" s="1">
-        <f t="shared" si="99"/>
-        <v>81.800449397303552</v>
+        <f t="shared" si="83"/>
+        <v>81.297903659385653</v>
       </c>
       <c r="CO41" s="1">
-        <f t="shared" si="99"/>
-        <v>80.982444903330517</v>
+        <f t="shared" si="83"/>
+        <v>80.484924622791794</v>
       </c>
       <c r="CP41" s="1">
-        <f t="shared" ref="CP41:ES41" si="100">CO41*(1+$AE$22)</f>
-        <v>80.172620454297217</v>
+        <f t="shared" ref="CP41:ES41" si="84">CO41*(1+$AE$22)</f>
+        <v>79.680075376563877</v>
       </c>
       <c r="CQ41" s="1">
-        <f t="shared" si="100"/>
-        <v>79.370894249754244</v>
+        <f t="shared" si="84"/>
+        <v>78.88327462279824</v>
       </c>
       <c r="CR41" s="1">
-        <f t="shared" si="100"/>
-        <v>78.577185307256698</v>
+        <f t="shared" si="84"/>
+        <v>78.094441876570258</v>
       </c>
       <c r="CS41" s="1">
-        <f t="shared" si="100"/>
-        <v>77.791413454184138</v>
+        <f t="shared" si="84"/>
+        <v>77.313497457804559</v>
       </c>
       <c r="CT41" s="1">
-        <f t="shared" si="100"/>
-        <v>77.013499319642293</v>
+        <f t="shared" si="84"/>
+        <v>76.540362483226517</v>
       </c>
       <c r="CU41" s="1">
-        <f t="shared" si="100"/>
-        <v>76.243364326445871</v>
+        <f t="shared" si="84"/>
+        <v>75.774958858394257</v>
       </c>
       <c r="CV41" s="1">
-        <f t="shared" si="100"/>
-        <v>75.480930683181413</v>
+        <f t="shared" si="84"/>
+        <v>75.017209269810309</v>
       </c>
       <c r="CW41" s="1">
-        <f t="shared" si="100"/>
-        <v>74.726121376349596</v>
+        <f t="shared" si="84"/>
+        <v>74.267037177112201</v>
       </c>
       <c r="CX41" s="1">
-        <f t="shared" si="100"/>
-        <v>73.978860162586102</v>
+        <f t="shared" si="84"/>
+        <v>73.524366805341074</v>
       </c>
       <c r="CY41" s="1">
-        <f t="shared" si="100"/>
-        <v>73.239071560960241</v>
+        <f t="shared" si="84"/>
+        <v>72.78912313728766</v>
       </c>
       <c r="CZ41" s="1">
-        <f t="shared" si="100"/>
-        <v>72.506680845350644</v>
+        <f t="shared" si="84"/>
+        <v>72.061231905914781</v>
       </c>
       <c r="DA41" s="1">
-        <f t="shared" si="100"/>
-        <v>71.781614036897139</v>
+        <f t="shared" si="84"/>
+        <v>71.340619586855638</v>
       </c>
       <c r="DB41" s="1">
-        <f t="shared" si="100"/>
-        <v>71.063797896528172</v>
+        <f t="shared" si="84"/>
+        <v>70.62721339098708</v>
       </c>
       <c r="DC41" s="1">
-        <f t="shared" si="100"/>
-        <v>70.353159917562891</v>
+        <f t="shared" si="84"/>
+        <v>69.920941257077203</v>
       </c>
       <c r="DD41" s="1">
-        <f t="shared" si="100"/>
-        <v>69.649628318387258</v>
+        <f t="shared" si="84"/>
+        <v>69.221731844506436</v>
       </c>
       <c r="DE41" s="1">
-        <f t="shared" si="100"/>
-        <v>68.953132035203382</v>
+        <f t="shared" si="84"/>
+        <v>68.529514526061377</v>
       </c>
       <c r="DF41" s="1">
-        <f t="shared" si="100"/>
-        <v>68.26360071485135</v>
+        <f t="shared" si="84"/>
+        <v>67.844219380800766</v>
       </c>
       <c r="DG41" s="1">
-        <f t="shared" si="100"/>
-        <v>67.580964707702833</v>
+        <f t="shared" si="84"/>
+        <v>67.165777186992756</v>
       </c>
       <c r="DH41" s="1">
-        <f t="shared" si="100"/>
-        <v>66.905155060625802</v>
+        <f t="shared" si="84"/>
+        <v>66.494119415122825</v>
       </c>
       <c r="DI41" s="1">
-        <f t="shared" si="100"/>
-        <v>66.236103510019547</v>
+        <f t="shared" si="84"/>
+        <v>65.829178220971599</v>
       </c>
       <c r="DJ41" s="1">
-        <f t="shared" si="100"/>
-        <v>65.573742474919356</v>
+        <f t="shared" si="84"/>
+        <v>65.170886438761883</v>
       </c>
       <c r="DK41" s="1">
-        <f t="shared" si="100"/>
-        <v>64.918005050170166</v>
+        <f t="shared" si="84"/>
+        <v>64.519177574374268</v>
       </c>
       <c r="DL41" s="1">
-        <f t="shared" si="100"/>
-        <v>64.268824999668468</v>
+        <f t="shared" si="84"/>
+        <v>63.873985798630528</v>
       </c>
       <c r="DM41" s="1">
-        <f t="shared" si="100"/>
-        <v>63.62613674967178</v>
+        <f t="shared" si="84"/>
+        <v>63.235245940644219</v>
       </c>
       <c r="DN41" s="1">
-        <f t="shared" si="100"/>
-        <v>62.989875382175065</v>
+        <f t="shared" si="84"/>
+        <v>62.602893481237778</v>
       </c>
       <c r="DO41" s="1">
-        <f t="shared" si="100"/>
-        <v>62.359976628353316</v>
+        <f t="shared" si="84"/>
+        <v>61.976864546425404</v>
       </c>
       <c r="DP41" s="1">
-        <f t="shared" si="100"/>
-        <v>61.736376862069783</v>
+        <f t="shared" si="84"/>
+        <v>61.357095900961149</v>
       </c>
       <c r="DQ41" s="1">
-        <f t="shared" si="100"/>
-        <v>61.119013093449084</v>
+        <f t="shared" si="84"/>
+        <v>60.743524941951534</v>
       </c>
       <c r="DR41" s="1">
-        <f t="shared" si="100"/>
-        <v>60.507822962514595</v>
+        <f t="shared" si="84"/>
+        <v>60.136089692532018</v>
       </c>
       <c r="DS41" s="1">
-        <f t="shared" si="100"/>
-        <v>59.902744732889445</v>
+        <f t="shared" si="84"/>
+        <v>59.534728795606696</v>
       </c>
       <c r="DT41" s="1">
-        <f t="shared" si="100"/>
-        <v>59.303717285560552</v>
+        <f t="shared" si="84"/>
+        <v>58.93938150765063</v>
       </c>
       <c r="DU41" s="1">
-        <f t="shared" si="100"/>
-        <v>58.710680112704949</v>
+        <f t="shared" si="84"/>
+        <v>58.349987692574125</v>
       </c>
       <c r="DV41" s="1">
-        <f t="shared" si="100"/>
-        <v>58.1235733115779</v>
+        <f t="shared" si="84"/>
+        <v>57.766487815648382</v>
       </c>
       <c r="DW41" s="1">
-        <f t="shared" si="100"/>
-        <v>57.542337578462117</v>
+        <f t="shared" si="84"/>
+        <v>57.188822937491899</v>
       </c>
       <c r="DX41" s="1">
-        <f t="shared" si="100"/>
-        <v>56.966914202677494</v>
+        <f t="shared" si="84"/>
+        <v>56.616934708116979</v>
       </c>
       <c r="DY41" s="1">
-        <f t="shared" si="100"/>
-        <v>56.397245060650718</v>
+        <f t="shared" si="84"/>
+        <v>56.050765361035808</v>
       </c>
       <c r="DZ41" s="1">
-        <f t="shared" si="100"/>
-        <v>55.833272610044212</v>
+        <f t="shared" si="84"/>
+        <v>55.490257707425449</v>
       </c>
       <c r="EA41" s="1">
-        <f t="shared" si="100"/>
-        <v>55.274939883943766</v>
+        <f t="shared" si="84"/>
+        <v>54.935355130351198</v>
       </c>
       <c r="EB41" s="1">
-        <f t="shared" si="100"/>
-        <v>54.722190485104328</v>
+        <f t="shared" si="84"/>
+        <v>54.386001579047687</v>
       </c>
       <c r="EC41" s="1">
-        <f t="shared" si="100"/>
-        <v>54.174968580253285</v>
+        <f t="shared" si="84"/>
+        <v>53.842141563257208</v>
       </c>
       <c r="ED41" s="1">
-        <f t="shared" si="100"/>
-        <v>53.633218894450749</v>
+        <f t="shared" si="84"/>
+        <v>53.303720147624638</v>
       </c>
       <c r="EE41" s="1">
-        <f t="shared" si="100"/>
-        <v>53.096886705506243</v>
+        <f t="shared" si="84"/>
+        <v>52.770682946148391</v>
       </c>
       <c r="EF41" s="1">
-        <f t="shared" si="100"/>
-        <v>52.565917838451178</v>
+        <f t="shared" si="84"/>
+        <v>52.242976116686904</v>
       </c>
       <c r="EG41" s="1">
-        <f t="shared" si="100"/>
-        <v>52.040258660066662</v>
+        <f t="shared" si="84"/>
+        <v>51.720546355520035</v>
       </c>
       <c r="EH41" s="1">
-        <f t="shared" si="100"/>
-        <v>51.519856073465995</v>
+        <f t="shared" si="84"/>
+        <v>51.203340891964835</v>
       </c>
       <c r="EI41" s="1">
-        <f t="shared" si="100"/>
-        <v>51.004657512731335</v>
+        <f t="shared" si="84"/>
+        <v>50.691307483045186</v>
       </c>
       <c r="EJ41" s="1">
-        <f t="shared" si="100"/>
-        <v>50.494610937604023</v>
+        <f t="shared" si="84"/>
+        <v>50.184394408214736</v>
       </c>
       <c r="EK41" s="1">
-        <f t="shared" si="100"/>
-        <v>49.98966482822798</v>
+        <f t="shared" si="84"/>
+        <v>49.682550464132589</v>
       </c>
       <c r="EL41" s="1">
-        <f t="shared" si="100"/>
-        <v>49.489768179945699</v>
+        <f t="shared" si="84"/>
+        <v>49.18572495949126</v>
       </c>
       <c r="EM41" s="1">
-        <f t="shared" si="100"/>
-        <v>48.994870498146241</v>
+        <f t="shared" si="84"/>
+        <v>48.693867709896345</v>
       </c>
       <c r="EN41" s="1">
-        <f t="shared" si="100"/>
-        <v>48.504921793164776</v>
+        <f t="shared" si="84"/>
+        <v>48.206929032797383</v>
       </c>
       <c r="EO41" s="1">
-        <f t="shared" si="100"/>
-        <v>48.01987257523313</v>
+        <f t="shared" si="84"/>
+        <v>47.724859742469405</v>
       </c>
       <c r="EP41" s="1">
-        <f t="shared" si="100"/>
-        <v>47.539673849480799</v>
+        <f t="shared" si="84"/>
+        <v>47.247611145044708</v>
       </c>
       <c r="EQ41" s="1">
-        <f t="shared" si="100"/>
-        <v>47.064277110985991</v>
+        <f t="shared" si="84"/>
+        <v>46.77513503359426</v>
       </c>
       <c r="ER41" s="1">
-        <f t="shared" si="100"/>
-        <v>46.593634339876132</v>
+        <f t="shared" si="84"/>
+        <v>46.307383683258315</v>
       </c>
       <c r="ES41" s="1">
-        <f t="shared" si="100"/>
-        <v>46.127697996477373</v>
+        <f t="shared" si="84"/>
+        <v>45.84430984642573</v>
       </c>
     </row>
     <row r="42" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5244,11 +5251,11 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" ref="I45:J47" si="101">I35/E35-1</f>
+        <f>I35/E35-1</f>
         <v>0.125</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="101"/>
+        <f>J35/F35-1</f>
         <v>0.16883116883116878</v>
       </c>
       <c r="O45" s="9">
@@ -5264,47 +5271,47 @@
         <v>0.30327868852459017</v>
       </c>
       <c r="R45" s="9">
-        <f t="shared" ref="R45:AB45" si="102">R35/Q35-1</f>
+        <f>R35/Q35-1</f>
         <v>0.10062893081761004</v>
       </c>
       <c r="S45" s="9">
-        <f t="shared" si="102"/>
+        <f>S35/R35-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" si="102"/>
+        <f>T35/S35-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="U45" s="9">
-        <f t="shared" si="102"/>
+        <f>U35/T35-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="V45" s="9">
-        <f t="shared" si="102"/>
+        <f>V35/U35-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W45" s="9">
-        <f t="shared" si="102"/>
+        <f>W35/V35-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="102"/>
+        <f>X35/W35-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y45" s="9">
-        <f t="shared" si="102"/>
+        <f>Y35/X35-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z45" s="9">
-        <f t="shared" si="102"/>
+        <f>Z35/Y35-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA45" s="9">
-        <f t="shared" si="102"/>
+        <f>AA35/Z35-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB45" s="9">
-        <f t="shared" si="102"/>
+        <f>AB35/AA35-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD45" t="s">
@@ -5312,7 +5319,7 @@
       </c>
       <c r="AE45" s="5">
         <f>NPV(AE23,R41:ES41)</f>
-        <v>1210.5100143041536</v>
+        <v>1204.2231297073492</v>
       </c>
     </row>
     <row r="46" spans="2:149" x14ac:dyDescent="0.3">
@@ -5320,23 +5327,23 @@
         <v>59</v>
       </c>
       <c r="G46" s="9">
-        <f t="shared" ref="G46:H47" si="103">G36/C36-1</f>
+        <f>G36/C36-1</f>
         <v>-2.2727272727272818E-2</v>
       </c>
       <c r="H46" s="9">
-        <f t="shared" si="103"/>
+        <f>H36/D36-1</f>
         <v>6.9767441860465018E-2</v>
       </c>
       <c r="I46" s="9">
-        <f t="shared" si="101"/>
+        <f>I36/E36-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="101"/>
+        <f>J36/F36-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="O46" s="9">
-        <f t="shared" ref="O46" si="104">O36/N36-1</f>
+        <f t="shared" ref="O46" si="85">O36/N36-1</f>
         <v>-9.9476439790575966E-2</v>
       </c>
       <c r="P46" s="9">
@@ -5348,47 +5355,47 @@
         <v>1.156069364161838E-2</v>
       </c>
       <c r="R46" s="9">
-        <f t="shared" ref="R46:AB46" si="105">R36/Q36-1</f>
+        <f t="shared" ref="R46:AB46" si="86">R36/Q36-1</f>
         <v>3.6571428571428699E-2</v>
       </c>
       <c r="S46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="T46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="U46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="V46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB46" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD46" t="s">
@@ -5396,7 +5403,7 @@
       </c>
       <c r="AE46" s="5">
         <f>Main!D8</f>
-        <v>-186.5</v>
+        <v>-174.5</v>
       </c>
     </row>
     <row r="47" spans="2:149" x14ac:dyDescent="0.3">
@@ -5404,19 +5411,19 @@
         <v>60</v>
       </c>
       <c r="G47" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="G47:H47" si="87">G37/C37-1</f>
         <v>0.1056910569105689</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="87"/>
         <v>9.6491228070175294E-2</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" ref="I47:J47" si="88">I37/E37-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="88"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="O47" s="9"/>
@@ -5438,7 +5445,7 @@
       </c>
       <c r="AE47" s="5">
         <f>AE45+AE46</f>
-        <v>1024.0100143041536</v>
+        <v>1029.7231297073492</v>
       </c>
     </row>
     <row r="48" spans="2:149" x14ac:dyDescent="0.3">
@@ -5447,7 +5454,7 @@
       </c>
       <c r="AE48" s="4">
         <f>AE47/AB18</f>
-        <v>36.441637519720771</v>
+        <v>33.651082670174809</v>
       </c>
     </row>
     <row r="49" spans="30:31" x14ac:dyDescent="0.3">
@@ -5456,7 +5463,7 @@
       </c>
       <c r="AE49" s="4">
         <f>Main!D3</f>
-        <v>17.52</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="50" spans="30:31" x14ac:dyDescent="0.3">

--- a/Financial Analysis/BAND.xlsx
+++ b/Financial Analysis/BAND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C09C42B-AD6C-4C30-99FD-264EA6EDCB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C509674-2D35-498D-A393-5113D687D8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{051CBDE9-D4CF-414F-808E-F0CC5F126926}"/>
   </bookViews>
@@ -217,7 +217,7 @@
     <t>CapEx</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -752,14 +752,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>16.11</v>
+        <v>12.96</v>
       </c>
       <c r="E3" s="3">
-        <v>45961</v>
+        <v>46070</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45961</v>
+        <v>46070</v>
       </c>
       <c r="G3" s="3">
         <v>46072</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>492.96600000000001</v>
+        <v>396.57600000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>667.46600000000001</v>
+        <v>571.07600000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2868,47 +2868,47 @@
         <v>28.1</v>
       </c>
       <c r="R18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" ref="R18:AB18" si="38">28.6+2</f>
         <v>30.6</v>
       </c>
       <c r="S18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="T18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="U18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="V18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="W18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="X18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="Y18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="Z18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="AA18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
       <c r="AB18" s="5">
-        <f>28.6+2</f>
+        <f t="shared" si="38"/>
         <v>30.6</v>
       </c>
     </row>
@@ -2917,103 +2917,103 @@
         <v>28</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:H19" si="38">C17/C18</f>
+        <f t="shared" ref="C19:H19" si="39">C17/C18</f>
         <v>-0.32384341637010666</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.14234875444839828</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.4234875444840159E-2</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-6.4056939501779459E-2</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-0.13523131672597843</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-0.16725978647686809</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" ref="I19:J19" si="39">I17/I18</f>
+        <f t="shared" ref="I19:J19" si="40">I17/I18</f>
         <v>-3.921568627450981E-2</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-6.9411764705882187E-2</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" ref="L19:S19" si="40">L17/L18</f>
+        <f t="shared" ref="L19:S19" si="41">L17/L18</f>
         <v>8.5409252669039024E-2</v>
       </c>
       <c r="M19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-1.5729537366548039</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-0.9786476868327405</v>
       </c>
       <c r="O19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.70106761565836473</v>
       </c>
       <c r="P19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-0.58362989323843495</v>
       </c>
       <c r="Q19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-0.23131672597864761</v>
       </c>
       <c r="R19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>-0.38640522875817029</v>
       </c>
       <c r="S19" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0009039215686268</v>
       </c>
       <c r="T19" s="7">
-        <f t="shared" ref="T19:AB19" si="41">T17/T18</f>
+        <f t="shared" ref="T19:AB19" si="42">T17/T18</f>
         <v>2.2163520392156832</v>
       </c>
       <c r="U19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.2643599368627449</v>
       </c>
       <c r="V19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.300641614756862</v>
       </c>
       <c r="W19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.3658780007533711</v>
       </c>
       <c r="X19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.4669921351670925</v>
       </c>
       <c r="Y19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.5705413923696918</v>
       </c>
       <c r="Z19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.6765723469357838</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.7851321708385584</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.8962686264161102</v>
       </c>
     </row>
@@ -3032,16 +3032,16 @@
         <v>3.6866359447004671E-2</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" ref="I21:J21" si="42">I3/E3-1</f>
+        <f t="shared" ref="I21:J21" si="43">I3/E3-1</f>
         <v>-1.0314595152140282E-2</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9">
-        <f t="shared" ref="M21" si="43">M3/L3-1</f>
+        <f t="shared" ref="M21" si="44">M3/L3-1</f>
         <v>0.47506448839208959</v>
       </c>
       <c r="N21" s="9">
@@ -3065,43 +3065,43 @@
         <v>7.4816299265196839E-3</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:AB21" si="44">S3/R3-1</f>
+        <f t="shared" ref="S21:AB21" si="45">S3/R3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3110,43 +3110,43 @@
         <v>36</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:H22" si="45">C5/C3</f>
+        <f t="shared" ref="C22:H22" si="46">C5/C3</f>
         <v>0.38304093567251463</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.37327188940092165</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.37751418256833419</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.36428571428571427</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.41078600114744696</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.39833333333333337</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22:J22" si="46">I5/I3</f>
+        <f t="shared" ref="I22:J22" si="47">I5/I3</f>
         <v>0.38457529963522674</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.39</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22:M22" si="47">L5/L3</f>
+        <f t="shared" ref="L22:M22" si="48">L5/L3</f>
         <v>0.46259673258813411</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.45992422034392305</v>
       </c>
       <c r="N22" s="9">
@@ -3170,43 +3170,43 @@
         <v>0.39541307518896696</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:AB22" si="48">S5/S3</f>
+        <f t="shared" ref="S22:AB22" si="49">S5/S3</f>
         <v>0.42</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43000000000000005</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43000000000000005</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
       <c r="AD22" t="s">
@@ -3233,16 +3233,16 @@
         <v>0.12811387900355853</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23:J23" si="49">I6/E6-1</f>
+        <f t="shared" ref="I23:J23" si="50">I6/E6-1</f>
         <v>9.27152317880795E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="L23" s="9"/>
       <c r="M23" s="9">
-        <f t="shared" ref="M23" si="50">M6/L6-1</f>
+        <f t="shared" ref="M23" si="51">M6/L6-1</f>
         <v>0.33650793650793664</v>
       </c>
       <c r="N23" s="9">
@@ -3266,43 +3266,43 @@
         <v>8.682967959527832E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:AB23" si="51">S6/R6-1</f>
+        <f t="shared" ref="S23:AB23" si="52">S6/R6-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD23" t="s">
@@ -3317,43 +3317,43 @@
         <v>38</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:H24" si="52">C7/C3</f>
+        <f t="shared" ref="C24:H24" si="53">C7/C3</f>
         <v>0.17017543859649123</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.15034562211981567</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13563692625064466</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13428571428571429</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.15203671830177853</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13777777777777778</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24:J24" si="53">I7/I3</f>
+        <f t="shared" ref="I24:J24" si="54">I7/I3</f>
         <v>0.12871287128712872</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.13</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" ref="L24:M24" si="54">L7/L3</f>
+        <f t="shared" ref="L24:M24" si="55">L7/L3</f>
         <v>0.15047291487532244</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.1183328475663072</v>
       </c>
       <c r="N24" s="9">
@@ -3377,43 +3377,43 @@
         <v>0.13662246386420898</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:AB24" si="55">S7/S3</f>
+        <f t="shared" ref="S24:AB24" si="56">S7/S3</f>
         <v>0.13</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13</v>
       </c>
       <c r="AD24" t="s">
@@ -3441,16 +3441,16 @@
         <v>0.12574850299401197</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" ref="I25:J25" si="56">I8/E8-1</f>
+        <f t="shared" ref="I25:J25" si="57">I8/E8-1</f>
         <v>2.8409090909090828E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9">
-        <f t="shared" ref="M25" si="57">M8/L8-1</f>
+        <f t="shared" ref="M25" si="58">M8/L8-1</f>
         <v>0.51020408163265318</v>
       </c>
       <c r="N25" s="9">
@@ -3474,43 +3474,43 @@
         <v>6.8061366806136725E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:AB25" si="58">S8/R8-1</f>
+        <f t="shared" ref="S25:AB25" si="59">S8/R8-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD25" t="s">
@@ -3526,43 +3526,43 @@
         <v>40</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:H26" si="59">C10/C3</f>
+        <f t="shared" ref="C26:H26" si="60">C10/C3</f>
         <v>-6.0233918128654952E-2</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-3.5138248847926316E-2</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-4.6415678184630813E-3</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.2857142857142871E-2</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-2.6391279403327562E-2</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.9999999999999969E-2</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" ref="I26:J26" si="60">I10/I3</f>
+        <f t="shared" ref="I26:J26" si="61">I10/I3</f>
         <v>-1.0422094841063054E-2</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-5.9644059644057342E-4</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" ref="L26:M26" si="61">L10/L3</f>
+        <f t="shared" ref="L26:M26" si="62">L10/L3</f>
         <v>-7.6096302665520227E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-3.9930049548236632E-2</v>
       </c>
       <c r="N26" s="9">
@@ -3586,43 +3586,43 @@
         <v>-1.369049197719137E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:AB26" si="62">S10/S3</f>
+        <f t="shared" ref="S26:AB26" si="63">S10/S3</f>
         <v>8.3013721069915808E-2</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>8.9956300405916206E-2</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.020037416162266E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>8.9969140756711183E-2</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.0785155707357082E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.283628163179472E-2</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.4867298478541806E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.6878403395418797E-2</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9.8869791597424525E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.10084165638568515</v>
       </c>
       <c r="AD26" t="s">
@@ -3638,43 +3638,43 @@
         <v>26</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:H27" si="63">C16/C15</f>
+        <f t="shared" ref="C27:H27" si="64">C16/C15</f>
         <v>2.150537634408603E-2</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-8.1081081081081252E-2</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.3333333333333992</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.39999999999999963</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-2.7027027027027074E-2</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-2.1739130434782636E-2</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" ref="I27:J27" si="64">I16/I15</f>
+        <f t="shared" ref="I27:J27" si="65">I16/I15</f>
         <v>0.65714285714285714</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" ref="L27:M27" si="65">L16/L15</f>
+        <f t="shared" ref="L27:M27" si="66">L16/L15</f>
         <v>1.1568627450980389</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-0.51369863013698647</v>
       </c>
       <c r="N27" s="9">
@@ -3698,43 +3698,43 @@
         <v>0.15081873024992803</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" ref="S27:AB27" si="66">S16/S15</f>
+        <f t="shared" ref="S27:AB27" si="67">S16/S15</f>
         <v>0</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AD27" t="s">
@@ -3750,43 +3750,43 @@
         <v>41</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:H28" si="67">C17/C3</f>
+        <f t="shared" ref="C28:H28" si="68">C17/C3</f>
         <v>-5.3216374269005835E-2</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>2.3041474654377836E-2</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>2.0629190304280991E-3</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-8.571428571428584E-3</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-2.1801491681009717E-2</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-2.6111111111111078E-2</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" ref="I28:J28" si="68">I17/I3</f>
+        <f t="shared" ref="I28:J28" si="69">I17/I3</f>
         <v>-6.253256904637833E-3</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.0216450216450193E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" ref="L28:M28" si="69">L17/L3</f>
+        <f t="shared" ref="L28:M28" si="70">L17/L3</f>
         <v>1.0318142734307811E-2</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.1288254153308073</v>
       </c>
       <c r="N28" s="9">
@@ -3810,43 +3810,43 @@
         <v>-1.5679618087786781E-2</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28:AB28" si="70">S17/S3</f>
+        <f t="shared" ref="S28:AB28" si="71">S17/S3</f>
         <v>7.9601004703698186E-2</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.6443210028927478E-2</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.6583957597075434E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.6246358999089043E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.6952880368628402E-2</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.8891292312515219E-2</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>9.0806280061636435E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>9.2697943260369134E-2</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>9.456637675252047E-2</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>9.6411670515930983E-2</v>
       </c>
       <c r="AD28" t="s">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AE28" s="4">
         <f>Main!D3</f>
-        <v>16.11</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="29" spans="2:141" x14ac:dyDescent="0.3">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AE29" s="10">
         <f>AE27/AE28-1</f>
-        <v>-0.1218687557745094</v>
+        <v>9.1565921641408421E-2</v>
       </c>
     </row>
     <row r="30" spans="2:141" x14ac:dyDescent="0.3">
@@ -3879,23 +3879,23 @@
         <v>52</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:G32" si="71">C17</f>
+        <f t="shared" ref="C32:G32" si="72">C17</f>
         <v>-9.0999999999999979</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3.999999999999992</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.40000000000000846</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-1.8000000000000027</v>
       </c>
       <c r="G32" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-3.799999999999994</v>
       </c>
       <c r="H32" s="8">
@@ -3903,71 +3903,71 @@
         <v>-4.699999999999994</v>
       </c>
       <c r="I32" s="11">
-        <f t="shared" ref="I32:J32" si="72">I17</f>
+        <f t="shared" ref="I32:J32" si="73">I17</f>
         <v>-1.2000000000000002</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>-2.1239999999999952</v>
       </c>
       <c r="N32" s="8">
-        <f t="shared" ref="N32:O32" si="73">N17</f>
+        <f t="shared" ref="N32:O32" si="74">N17</f>
         <v>-27.500000000000011</v>
       </c>
       <c r="O32" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>19.700000000000049</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" ref="P32:R32" si="74">P17</f>
+        <f t="shared" ref="P32:R32" si="75">P17</f>
         <v>-16.400000000000023</v>
       </c>
       <c r="Q32" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>-6.4999999999999982</v>
       </c>
       <c r="R32" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>-11.824000000000012</v>
       </c>
       <c r="S32" s="8">
-        <f t="shared" ref="S32:AB32" si="75">S17</f>
+        <f t="shared" ref="S32:AB32" si="76">S17</f>
         <v>61.227659999999979</v>
       </c>
       <c r="T32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>67.820372399999911</v>
       </c>
       <c r="U32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>69.289414067999999</v>
       </c>
       <c r="V32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>70.399633411559975</v>
       </c>
       <c r="W32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>72.395866823053154</v>
       </c>
       <c r="X32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>75.489959336113031</v>
       </c>
       <c r="Y32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>78.658566606512579</v>
       </c>
       <c r="Z32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>81.903113816234992</v>
       </c>
       <c r="AA32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>85.225044427659896</v>
       </c>
       <c r="AB32" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>88.625819968332976</v>
       </c>
     </row>
@@ -4085,51 +4085,51 @@
         <v>0.8</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" ref="Q34:Q40" si="76">SUM(C34:F34)</f>
+        <f t="shared" ref="Q34:Q40" si="77">SUM(C34:F34)</f>
         <v>1.9000000000000001</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" ref="R34:R40" si="77">SUM(G34:J34)</f>
+        <f t="shared" ref="R34:R40" si="78">SUM(G34:J34)</f>
         <v>2.8</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" ref="S34:AB34" si="78">R34*1.05</f>
+        <f t="shared" ref="S34:AB34" si="79">R34*1.05</f>
         <v>2.94</v>
       </c>
       <c r="T34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.0870000000000002</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.2413500000000002</v>
       </c>
       <c r="V34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.4034175000000002</v>
       </c>
       <c r="W34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.5735883750000004</v>
       </c>
       <c r="X34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.7522677937500006</v>
       </c>
       <c r="Y34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.9398811834375009</v>
       </c>
       <c r="Z34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>4.136875242609376</v>
       </c>
       <c r="AA34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>4.3437190047398451</v>
       </c>
       <c r="AB34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>4.5609049549768379</v>
       </c>
     </row>
@@ -4171,11 +4171,11 @@
         <v>24.4</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>31.8</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>35</v>
       </c>
       <c r="S35" s="5">
@@ -4195,7 +4195,7 @@
         <v>40.153931999999998</v>
       </c>
       <c r="W35" s="5">
-        <f t="shared" ref="W35" si="79">V35*1.02</f>
+        <f t="shared" ref="W35" si="80">V35*1.02</f>
         <v>40.95701064</v>
       </c>
       <c r="X35" s="5">
@@ -4203,19 +4203,19 @@
         <v>41.366580746400004</v>
       </c>
       <c r="Y35" s="5">
-        <f t="shared" ref="Y35:AB35" si="80">X35*1.01</f>
+        <f t="shared" ref="Y35:AB35" si="81">X35*1.01</f>
         <v>41.780246553864004</v>
       </c>
       <c r="Z35" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>42.198049019402646</v>
       </c>
       <c r="AA35" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>42.620029509596669</v>
       </c>
       <c r="AB35" s="5">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>43.046229804692636</v>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
         <v>17.3</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>17.5</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>18.14</v>
       </c>
       <c r="S36" s="5">
@@ -4271,39 +4271,39 @@
         <v>18.502800000000001</v>
       </c>
       <c r="T36" s="5">
-        <f t="shared" ref="T36:AB36" si="81">S36*1.01</f>
+        <f t="shared" ref="T36:AB36" si="82">S36*1.01</f>
         <v>18.687828</v>
       </c>
       <c r="U36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>18.874706279999998</v>
       </c>
       <c r="V36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>19.063453342799999</v>
       </c>
       <c r="W36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>19.254087876227999</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>19.446628754990279</v>
       </c>
       <c r="Y36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>19.641095042540183</v>
       </c>
       <c r="Z36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>19.837505992965585</v>
       </c>
       <c r="AA36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>20.035881052895242</v>
       </c>
       <c r="AB36" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>20.236239863424196</v>
       </c>
     </row>
@@ -4347,11 +4347,11 @@
         <v>37</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>48.3</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>53.16</v>
       </c>
       <c r="S37" s="5"/>
@@ -4403,11 +4403,11 @@
         <v>4</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>2.5</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="S38" s="5">
@@ -4479,51 +4479,51 @@
         <v>-12.8</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-10.3</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-1.1000000000000001</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:AB39" si="82">R39*1.05</f>
+        <f t="shared" ref="S39:AB39" si="83">R39*1.05</f>
         <v>-1.1550000000000002</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.2127500000000002</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.2733875000000003</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.3370568750000005</v>
       </c>
       <c r="W39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.4039097187500005</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.4741052046875005</v>
       </c>
       <c r="Y39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.5478104649218756</v>
       </c>
       <c r="Z39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.6252009881679694</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.706461037576368</v>
       </c>
       <c r="AB39" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-1.7917840894551864</v>
       </c>
     </row>
@@ -4566,11 +4566,11 @@
         <v>-3.2</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-0.5</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.8</v>
       </c>
       <c r="S40" s="5">
@@ -4609,95 +4609,95 @@
         <v>53</v>
       </c>
       <c r="C41" s="8">
-        <f>C32+SUM(C33:C40)</f>
+        <f t="shared" ref="C41:J41" si="84">C32+SUM(C33:C40)</f>
         <v>16.200000000000003</v>
       </c>
       <c r="D41" s="8">
-        <f>D32+SUM(D33:D40)</f>
+        <f t="shared" si="84"/>
         <v>18.79999999999999</v>
       </c>
       <c r="E41" s="8">
-        <f>E32+SUM(E33:E40)</f>
+        <f t="shared" si="84"/>
         <v>23.900000000000009</v>
       </c>
       <c r="F41" s="8">
-        <f>F32+SUM(F33:F40)</f>
+        <f t="shared" si="84"/>
         <v>23.399999999999995</v>
       </c>
       <c r="G41" s="8">
-        <f>G32+SUM(G33:G40)</f>
+        <f t="shared" si="84"/>
         <v>22.100000000000005</v>
       </c>
       <c r="H41" s="8">
-        <f>H32+SUM(H33:H40)</f>
+        <f t="shared" si="84"/>
         <v>22.100000000000009</v>
       </c>
       <c r="I41" s="11">
-        <f>I32+SUM(I33:I40)</f>
+        <f t="shared" si="84"/>
         <v>25.76</v>
       </c>
       <c r="J41" s="8">
-        <f>J32+SUM(J33:J40)</f>
+        <f t="shared" si="84"/>
         <v>27.016000000000005</v>
       </c>
       <c r="N41" s="8">
-        <f>N32+SUM(N33:N40)</f>
+        <f t="shared" ref="N41:AB41" si="85">N32+SUM(N33:N40)</f>
         <v>49.399999999999977</v>
       </c>
       <c r="O41" s="8">
-        <f>O32+SUM(O33:O40)</f>
+        <f t="shared" si="85"/>
         <v>34.700000000000045</v>
       </c>
       <c r="P41" s="8">
-        <f>P32+SUM(P33:P40)</f>
+        <f t="shared" si="85"/>
         <v>48.09999999999998</v>
       </c>
       <c r="Q41" s="8">
-        <f>Q32+SUM(Q33:Q40)</f>
+        <f t="shared" si="85"/>
         <v>82.3</v>
       </c>
       <c r="R41" s="8">
-        <f>R32+SUM(R33:R40)</f>
+        <f t="shared" si="85"/>
         <v>96.975999999999985</v>
       </c>
       <c r="S41" s="8">
-        <f>S32+SUM(S33:S40)</f>
+        <f t="shared" si="85"/>
         <v>118.26545999999998</v>
       </c>
       <c r="T41" s="8">
-        <f>T32+SUM(T33:T40)</f>
+        <f t="shared" si="85"/>
         <v>126.60245039999991</v>
       </c>
       <c r="U41" s="8">
-        <f>U32+SUM(U33:U40)</f>
+        <f t="shared" si="85"/>
         <v>129.49868284799999</v>
       </c>
       <c r="V41" s="8">
-        <f>V32+SUM(V33:V40)</f>
+        <f t="shared" si="85"/>
         <v>131.68337937935996</v>
       </c>
       <c r="W41" s="8">
-        <f>W32+SUM(W33:W40)</f>
+        <f t="shared" si="85"/>
         <v>134.77664399553115</v>
       </c>
       <c r="X41" s="8">
-        <f>X32+SUM(X33:X40)</f>
+        <f t="shared" si="85"/>
         <v>138.58133142656581</v>
       </c>
       <c r="Y41" s="8">
-        <f>Y32+SUM(Y33:Y40)</f>
+        <f t="shared" si="85"/>
         <v>142.4719789214324</v>
       </c>
       <c r="Z41" s="8">
-        <f>Z32+SUM(Z33:Z40)</f>
+        <f t="shared" si="85"/>
         <v>146.45034308304463</v>
       </c>
       <c r="AA41" s="8">
-        <f>AA32+SUM(AA33:AA40)</f>
+        <f t="shared" si="85"/>
         <v>150.51821295731526</v>
       </c>
       <c r="AB41" s="8">
-        <f>AB32+SUM(AB33:AB40)</f>
+        <f t="shared" si="85"/>
         <v>154.67741050197145</v>
       </c>
       <c r="AC41" s="1">
@@ -4705,483 +4705,483 @@
         <v>153.13063639695173</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" ref="AD41:CO41" si="83">AC41*(1+$AE$22)</f>
+        <f t="shared" ref="AD41:CO41" si="86">AC41*(1+$AE$22)</f>
         <v>151.59933003298221</v>
       </c>
       <c r="AE41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>150.08333673265238</v>
       </c>
       <c r="AF41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>148.58250336532586</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>147.09667833167259</v>
       </c>
       <c r="AH41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>145.62571154835587</v>
       </c>
       <c r="AI41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>144.1694544328723</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>142.72775988854357</v>
       </c>
       <c r="AK41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>141.30048228965813</v>
       </c>
       <c r="AL41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>139.88747746676154</v>
       </c>
       <c r="AM41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>138.48860269209393</v>
       </c>
       <c r="AN41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>137.10371666517298</v>
       </c>
       <c r="AO41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>135.73267949852126</v>
       </c>
       <c r="AP41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>134.37535270353604</v>
       </c>
       <c r="AQ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>133.03159917650066</v>
       </c>
       <c r="AR41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>131.70128318473564</v>
       </c>
       <c r="AS41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>130.38427035288828</v>
       </c>
       <c r="AT41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>129.08042764935939</v>
       </c>
       <c r="AU41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>127.7896233728658</v>
       </c>
       <c r="AV41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>126.51172713913715</v>
       </c>
       <c r="AW41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>125.24660986774578</v>
       </c>
       <c r="AX41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>123.99414376906832</v>
       </c>
       <c r="AY41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>122.75420233137763</v>
       </c>
       <c r="AZ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>121.52666030806385</v>
       </c>
       <c r="BA41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>120.31139370498322</v>
       </c>
       <c r="BB41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>119.10827976793338</v>
       </c>
       <c r="BC41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>117.91719697025405</v>
       </c>
       <c r="BD41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>116.73802500055152</v>
       </c>
       <c r="BE41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>115.57064475054599</v>
       </c>
       <c r="BF41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>114.41493830304053</v>
       </c>
       <c r="BG41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>113.27078892001012</v>
       </c>
       <c r="BH41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>112.13808103081001</v>
       </c>
       <c r="BI41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>111.01670022050192</v>
       </c>
       <c r="BJ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>109.9065332182969</v>
       </c>
       <c r="BK41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>108.80746788611393</v>
       </c>
       <c r="BL41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>107.71939320725279</v>
       </c>
       <c r="BM41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>106.64219927518026</v>
       </c>
       <c r="BN41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>105.57577728242846</v>
       </c>
       <c r="BO41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>104.52001950960418</v>
       </c>
       <c r="BP41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>103.47481931450814</v>
       </c>
       <c r="BQ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>102.44007112136306</v>
       </c>
       <c r="BR41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>101.41567041014943</v>
       </c>
       <c r="BS41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>100.40151370604794</v>
       </c>
       <c r="BT41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>99.397498568987459</v>
       </c>
       <c r="BU41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>98.403523583297584</v>
       </c>
       <c r="BV41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>97.419488347464608</v>
       </c>
       <c r="BW41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>96.445293463989955</v>
       </c>
       <c r="BX41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>95.480840529350061</v>
       </c>
       <c r="BY41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>94.526032124056556</v>
       </c>
       <c r="BZ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>93.580771802815988</v>
       </c>
       <c r="CA41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>92.64496408478783</v>
       </c>
       <c r="CB41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>91.718514443939952</v>
       </c>
       <c r="CC41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>90.801329299500551</v>
       </c>
       <c r="CD41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>89.893316006505543</v>
       </c>
       <c r="CE41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>88.994382846440487</v>
       </c>
       <c r="CF41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>88.104439017976077</v>
       </c>
       <c r="CG41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>87.22339462779631</v>
       </c>
       <c r="CH41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>86.351160681518351</v>
       </c>
       <c r="CI41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>85.487649074703171</v>
       </c>
       <c r="CJ41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>84.63277258395614</v>
       </c>
       <c r="CK41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>83.786444858116582</v>
       </c>
       <c r="CL41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>82.94858040953541</v>
       </c>
       <c r="CM41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>82.119094605440054</v>
       </c>
       <c r="CN41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>81.297903659385653</v>
       </c>
       <c r="CO41" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>80.484924622791794</v>
       </c>
       <c r="CP41" s="1">
-        <f t="shared" ref="CP41:ES41" si="84">CO41*(1+$AE$22)</f>
+        <f t="shared" ref="CP41:ES41" si="87">CO41*(1+$AE$22)</f>
         <v>79.680075376563877</v>
       </c>
       <c r="CQ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>78.88327462279824</v>
       </c>
       <c r="CR41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>78.094441876570258</v>
       </c>
       <c r="CS41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>77.313497457804559</v>
       </c>
       <c r="CT41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>76.540362483226517</v>
       </c>
       <c r="CU41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>75.774958858394257</v>
       </c>
       <c r="CV41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>75.017209269810309</v>
       </c>
       <c r="CW41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>74.267037177112201</v>
       </c>
       <c r="CX41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>73.524366805341074</v>
       </c>
       <c r="CY41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>72.78912313728766</v>
       </c>
       <c r="CZ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>72.061231905914781</v>
       </c>
       <c r="DA41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>71.340619586855638</v>
       </c>
       <c r="DB41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>70.62721339098708</v>
       </c>
       <c r="DC41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>69.920941257077203</v>
       </c>
       <c r="DD41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>69.221731844506436</v>
       </c>
       <c r="DE41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>68.529514526061377</v>
       </c>
       <c r="DF41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>67.844219380800766</v>
       </c>
       <c r="DG41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>67.165777186992756</v>
       </c>
       <c r="DH41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>66.494119415122825</v>
       </c>
       <c r="DI41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>65.829178220971599</v>
       </c>
       <c r="DJ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>65.170886438761883</v>
       </c>
       <c r="DK41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>64.519177574374268</v>
       </c>
       <c r="DL41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>63.873985798630528</v>
       </c>
       <c r="DM41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>63.235245940644219</v>
       </c>
       <c r="DN41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>62.602893481237778</v>
       </c>
       <c r="DO41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>61.976864546425404</v>
       </c>
       <c r="DP41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>61.357095900961149</v>
       </c>
       <c r="DQ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>60.743524941951534</v>
       </c>
       <c r="DR41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>60.136089692532018</v>
       </c>
       <c r="DS41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>59.534728795606696</v>
       </c>
       <c r="DT41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>58.93938150765063</v>
       </c>
       <c r="DU41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>58.349987692574125</v>
       </c>
       <c r="DV41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>57.766487815648382</v>
       </c>
       <c r="DW41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>57.188822937491899</v>
       </c>
       <c r="DX41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>56.616934708116979</v>
       </c>
       <c r="DY41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>56.050765361035808</v>
       </c>
       <c r="DZ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>55.490257707425449</v>
       </c>
       <c r="EA41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>54.935355130351198</v>
       </c>
       <c r="EB41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>54.386001579047687</v>
       </c>
       <c r="EC41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>53.842141563257208</v>
       </c>
       <c r="ED41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>53.303720147624638</v>
       </c>
       <c r="EE41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>52.770682946148391</v>
       </c>
       <c r="EF41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>52.242976116686904</v>
       </c>
       <c r="EG41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>51.720546355520035</v>
       </c>
       <c r="EH41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>51.203340891964835</v>
       </c>
       <c r="EI41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>50.691307483045186</v>
       </c>
       <c r="EJ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>50.184394408214736</v>
       </c>
       <c r="EK41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>49.682550464132589</v>
       </c>
       <c r="EL41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>49.18572495949126</v>
       </c>
       <c r="EM41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>48.693867709896345</v>
       </c>
       <c r="EN41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>48.206929032797383</v>
       </c>
       <c r="EO41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>47.724859742469405</v>
       </c>
       <c r="EP41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>47.247611145044708</v>
       </c>
       <c r="EQ41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>46.77513503359426</v>
       </c>
       <c r="ER41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>46.307383683258315</v>
       </c>
       <c r="ES41" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>45.84430984642573</v>
       </c>
     </row>
@@ -5243,75 +5243,75 @@
         <v>58</v>
       </c>
       <c r="G45" s="9">
-        <f>G35/C35-1</f>
+        <f t="shared" ref="G45:J46" si="88">G35/C35-1</f>
         <v>1.2345679012345734E-2</v>
       </c>
       <c r="H45" s="9">
-        <f>H35/D35-1</f>
+        <f t="shared" si="88"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="I45" s="9">
-        <f>I35/E35-1</f>
+        <f t="shared" si="88"/>
         <v>0.125</v>
       </c>
       <c r="J45" s="9">
-        <f>J35/F35-1</f>
+        <f t="shared" si="88"/>
         <v>0.16883116883116878</v>
       </c>
       <c r="O45" s="9">
-        <f>O35/N35-1</f>
+        <f t="shared" ref="O45:AB45" si="89">O35/N35-1</f>
         <v>5.1428571428571379E-2</v>
       </c>
       <c r="P45" s="9">
-        <f>P35/O35-1</f>
+        <f t="shared" si="89"/>
         <v>0.32608695652173925</v>
       </c>
       <c r="Q45" s="9">
-        <f>Q35/P35-1</f>
+        <f t="shared" si="89"/>
         <v>0.30327868852459017</v>
       </c>
       <c r="R45" s="9">
-        <f>R35/Q35-1</f>
+        <f t="shared" si="89"/>
         <v>0.10062893081761004</v>
       </c>
       <c r="S45" s="9">
-        <f>S35/R35-1</f>
+        <f t="shared" si="89"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="T45" s="9">
-        <f>T35/S35-1</f>
+        <f t="shared" si="89"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="U45" s="9">
-        <f>U35/T35-1</f>
+        <f t="shared" si="89"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="V45" s="9">
-        <f>V35/U35-1</f>
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W45" s="9">
-        <f>W35/V35-1</f>
+        <f t="shared" si="89"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X45" s="9">
-        <f>X35/W35-1</f>
+        <f t="shared" si="89"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y45" s="9">
-        <f>Y35/X35-1</f>
+        <f t="shared" si="89"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z45" s="9">
-        <f>Z35/Y35-1</f>
+        <f t="shared" si="89"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA45" s="9">
-        <f>AA35/Z35-1</f>
+        <f t="shared" si="89"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB45" s="9">
-        <f>AB35/AA35-1</f>
+        <f t="shared" si="89"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD45" t="s">
@@ -5327,23 +5327,23 @@
         <v>59</v>
       </c>
       <c r="G46" s="9">
-        <f>G36/C36-1</f>
+        <f t="shared" si="88"/>
         <v>-2.2727272727272818E-2</v>
       </c>
       <c r="H46" s="9">
-        <f>H36/D36-1</f>
+        <f t="shared" si="88"/>
         <v>6.9767441860465018E-2</v>
       </c>
       <c r="I46" s="9">
-        <f>I36/E36-1</f>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="J46" s="9">
-        <f>J36/F36-1</f>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="O46" s="9">
-        <f t="shared" ref="O46" si="85">O36/N36-1</f>
+        <f t="shared" ref="O46" si="90">O36/N36-1</f>
         <v>-9.9476439790575966E-2</v>
       </c>
       <c r="P46" s="9">
@@ -5355,47 +5355,47 @@
         <v>1.156069364161838E-2</v>
       </c>
       <c r="R46" s="9">
-        <f t="shared" ref="R46:AB46" si="86">R36/Q36-1</f>
+        <f t="shared" ref="R46:AB46" si="91">R36/Q36-1</f>
         <v>3.6571428571428699E-2</v>
       </c>
       <c r="S46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="T46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="U46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="V46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB46" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="91"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD46" t="s">
@@ -5411,19 +5411,19 @@
         <v>60</v>
       </c>
       <c r="G47" s="9">
-        <f t="shared" ref="G47:H47" si="87">G37/C37-1</f>
+        <f t="shared" ref="G47:H47" si="92">G37/C37-1</f>
         <v>0.1056910569105689</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>9.6491228070175294E-2</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" ref="I47:J47" si="88">I37/E37-1</f>
+        <f t="shared" ref="I47:J47" si="93">I37/E37-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="O47" s="9"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AE49" s="4">
         <f>Main!D3</f>
-        <v>16.11</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="50" spans="30:31" x14ac:dyDescent="0.3">
